--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcdigiuseppantonio/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D70B414-99B4-1849-A9DB-A98921DC334A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262CBD51-520E-C247-841E-D1FA2A27D9F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="520" windowWidth="28800" windowHeight="15900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2000" windowWidth="28800" windowHeight="15900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="207">
   <si>
     <t>LE SANCTUAIRE DES BRUMES</t>
   </si>
@@ -637,6 +637,12 @@
   </si>
   <si>
     <t>E15 - la serre</t>
+  </si>
+  <si>
+    <t>Suivez le chemin indiqué pour poursuivre l'enquête</t>
+  </si>
+  <si>
+    <t>Saisissez le nom de votre équipe ainsi que le nombre de joueur :</t>
   </si>
 </sst>
 </file>
@@ -2064,7 +2070,9 @@
       <c r="E4" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="25"/>
+      <c r="F4" s="12" t="s">
+        <v>206</v>
+      </c>
       <c r="G4" s="29"/>
     </row>
     <row r="5" spans="1:7" s="28" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -2290,8 +2298,8 @@
       <c r="E15" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="F15" s="41" t="s">
-        <v>116</v>
+      <c r="F15" s="40" t="s">
+        <v>120</v>
       </c>
       <c r="G15" s="40"/>
     </row>
@@ -2372,7 +2380,7 @@
       <c r="E19" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="F19" s="38" t="s">
+      <c r="F19" s="37" t="s">
         <v>120</v>
       </c>
       <c r="G19" s="37"/>
@@ -2973,7 +2981,9 @@
       <c r="E48" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="F48" s="37"/>
+      <c r="F48" s="37" t="s">
+        <v>205</v>
+      </c>
       <c r="G48" s="37"/>
     </row>
     <row r="49" spans="1:7" s="44" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -2992,7 +3002,9 @@
       <c r="E49" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="F49" s="43"/>
+      <c r="F49" s="43" t="s">
+        <v>205</v>
+      </c>
       <c r="G49" s="43"/>
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -3055,7 +3067,9 @@
       <c r="E52" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F52" s="12"/>
+      <c r="F52" s="12" t="s">
+        <v>119</v>
+      </c>
       <c r="G52" s="12" t="s">
         <v>153</v>
       </c>
@@ -3366,7 +3380,7 @@
         <v>173</v>
       </c>
       <c r="C67" s="34" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D67" s="35" t="s">
         <v>140</v>
@@ -3385,7 +3399,7 @@
         <v>173</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D68" s="11" t="s">
         <v>78</v>
@@ -3406,7 +3420,7 @@
         <v>173</v>
       </c>
       <c r="C69" s="37" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D69" s="37" t="s">
         <v>83</v>

--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Salle de seminaire</t>
+          <t>Aire de pique-nique, face aux ours polaires</t>
         </is>
       </c>
       <c r="E6" s="20" t="n"/>

--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>Indice : les cameras de surveillance</t>
+          <t>SOPHIE, CHEFFE DE LA SÉCURITÉ</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>Indice : les jumelles, la carcasse</t>
+          <t>L'ENCLOS DES LOUPS</t>
         </is>
       </c>
       <c r="C7" s="18" t="inlineStr">

--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -9,6 +9,7 @@
     <sheet name="Lisez-moi" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Parcours" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Textes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Quiz" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -106,8 +107,16 @@
       <sz val="8"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -168,6 +177,11 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F2430"/>
       </patternFill>
     </fill>
   </fills>
@@ -235,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -363,6 +377,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -663,13 +684,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="105" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="21" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -684,6 +706,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -705,10 +728,11 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>LES TROIS ONGLETS, EN BAS DE L'ECRAN</t>
+          <t>LES QUATRE ONGLETS, EN BAS DE L'ECRAN</t>
         </is>
       </c>
     </row>
@@ -733,85 +757,98 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>Quiz          ....  les questions du quiz animalier : une ligne par question, avec la minute de la video ou elle apparait</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>CE QUE TU DOIS REMPLIR</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="5" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">     Les cases sur fond creme sont a remplir par toi.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="6" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">     Les cases sur fond gris sont calculees ou fixees, tu peux les ignorer.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="7" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">     Les cases sur fond rose sont des questions qui attendent ta reponse.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>AVANCEMENT</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>AVANCEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>86 textes a ecrire au total, repartis sur les 17 etapes.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Astuce pour suivre ton avancement : clique sur la lettre F en haut de la colonne des textes, dans l'onglet Textes. En bas a droite de l'ecran, Excel affiche le nombre de cases remplies.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="3" t="inlineStr">
+    <row r="23"/>
+    <row r="24" ht="75" customHeight="1">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>QUATRE QUESTIONS AVANT QUE JE FABRIQUE QUOI QUE CE SOIT</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="75" customHeight="1">
-      <c r="B24" s="13" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">1. COMBIEN DE QR CODES ? </t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="B26" s="9" t="inlineStr">
+    <row r="26" ht="60" customHeight="1"/>
+    <row r="27">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>2. LES LETTRES DE L'ENIGME. En sens B, le joueur ramasse I, R, I, S dans cet ordre : le mot est deja ecrit, l'enigme du Jardin des Iris se resout sans reflechir. En sens A il ramasse R, I, S, I et doit chercher. Veux-tu permuter deux lettres pour reequilibrer ?</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="45" customHeight="1">
-      <c r="B28" s="9" t="inlineStr">
+    <row r="28" ht="45" customHeight="1"/>
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>3. LE CODE DE LA SERRE. Le joueur tape-t-il IRIS sur le site, ou sur un cadenas physique ? Si c'est sur le site, c'est une mecanique a construire, dis-le moi.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="75" customHeight="1">
-      <c r="B30" s="9" t="inlineStr">
+    <row r="30" ht="75" customHeight="1"/>
+    <row r="31">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>4. LES DEUX PISTES DE LA COLLEGUE SOIGNEUSE. Sur ton schema, elle ouvre deux branches : les cameras puis le plan d'un cote, les jumelles puis l'enclos des loups de l'autre. Les deux sont-elles obligatoires, ou la premiere est-elle facultative ? J'ai suppose qu'on les fait l'une apres l'autre.</t>
         </is>
@@ -2574,10 +2611,14 @@
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>QUIZ À METTRE EN PLACE en même temps que le tournage de la vidéo</t>
-        </is>
-      </c>
-      <c r="G29" s="12" t="n"/>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>Le quiz s'affiche sous la video de l'ecran 1. Les questions sont dans l'onglet Quiz.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="30" customFormat="1" customHeight="1" s="39">
       <c r="A30" s="38" t="inlineStr">
@@ -3906,4 +3947,179 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="47" t="inlineStr">
+        <is>
+          <t>LES QUESTIONS QUI SUIVENT UNE VIDÉO. Une ligne par question. « Apparait a » est le moment, dans la vidéo, où la question doit s'afficher : écrivez-le en minutes:secondes, par exemple 0:42. Les trois exemples ci-dessous sont à remplacer par vos vraies questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B2" s="48" t="inlineStr">
+        <is>
+          <t>Apparait a</t>
+        </is>
+      </c>
+      <c r="C2" s="48" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="D2" s="48" t="inlineStr">
+        <is>
+          <t>Proposition 1</t>
+        </is>
+      </c>
+      <c r="E2" s="48" t="inlineStr">
+        <is>
+          <t>Proposition 2</t>
+        </is>
+      </c>
+      <c r="F2" s="48" t="inlineStr">
+        <is>
+          <t>Proposition 3</t>
+        </is>
+      </c>
+      <c r="G2" s="48" t="inlineStr">
+        <is>
+          <t>Bonne reponse (1, 2 ou 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0:15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EXEMPLE — Combien de temps dort une panthère de l'Amour par jour ?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6 heures</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>12 heures</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>18 heures</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0:48</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EXEMPLE — Que mange-t-elle en priorité dans la nature ?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Des cerfs</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Des poissons</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Des baies</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1:20</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EXEMPLE — Combien en reste-t-il à l'état sauvage ?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Moins de 150</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Environ 3 000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Plus de 10 000</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -249,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -385,6 +385,15 @@
     <xf numFmtId="0" fontId="15" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -684,14 +693,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="B2:B31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="105" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="21" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -706,7 +714,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -728,7 +735,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -764,7 +770,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -793,7 +798,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -815,7 +819,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="75" customHeight="1">
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -3955,63 +3958,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46" customHeight="1">
-      <c r="A1" s="47" t="inlineStr">
-        <is>
-          <t>LES QUESTIONS QUI SUIVENT UNE VIDÉO. Une ligne par question. « Apparait a » est le moment, dans la vidéo, où la question doit s'afficher : écrivez-le en minutes:secondes, par exemple 0:42. Les trois exemples ci-dessous sont à remplacer par vos vraies questions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="48" t="inlineStr">
+    <row r="1" ht="58" customHeight="1">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>LES QUESTIONS QUI SUIVENT UNE VIDÉO. Une ligne par question. « Apparait a » = la minute de la vidéo où la question s'affiche (écrire 1:13). Le groupe a 10 secondes pour répondre, puis la question se verrouille et montre la bonne réponse. Laisser au moins 13 secondes entre deux questions. Une proposition laissée vide est simplement ignorée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B2" s="48" t="inlineStr">
+      <c r="B2" s="51" t="inlineStr">
         <is>
           <t>Apparait a</t>
         </is>
       </c>
-      <c r="C2" s="48" t="inlineStr">
+      <c r="C2" s="51" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="D2" s="48" t="inlineStr">
+      <c r="D2" s="51" t="inlineStr">
         <is>
           <t>Proposition 1</t>
         </is>
       </c>
-      <c r="E2" s="48" t="inlineStr">
+      <c r="E2" s="51" t="inlineStr">
         <is>
           <t>Proposition 2</t>
         </is>
       </c>
-      <c r="F2" s="48" t="inlineStr">
+      <c r="F2" s="51" t="inlineStr">
         <is>
           <t>Proposition 3</t>
         </is>
       </c>
-      <c r="G2" s="48" t="inlineStr">
-        <is>
-          <t>Bonne reponse (1, 2 ou 3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+      <c r="G2" s="51" t="inlineStr">
+        <is>
+          <t>Proposition 4</t>
+        </is>
+      </c>
+      <c r="H2" s="51" t="inlineStr">
+        <is>
+          <t>Bonne reponse (le numero de la proposition)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>E06</t>
@@ -4019,106 +4028,321 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0:15</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>EXEMPLE — Combien de temps dort une panthère de l'Amour par jour ?</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>6 heures</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>12 heures</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>18 heures</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+          <t>0:35</t>
+        </is>
+      </c>
+      <c r="C3" s="52" t="inlineStr">
+        <is>
+          <t>Bruit d'humain ou d'animal ?</t>
+        </is>
+      </c>
+      <c r="D3" s="52" t="inlineStr">
+        <is>
+          <t>Un coq</t>
+        </is>
+      </c>
+      <c r="E3" s="52" t="inlineStr">
+        <is>
+          <t>Un cri d'humain</t>
+        </is>
+      </c>
+      <c r="F3" s="52" t="inlineStr">
+        <is>
+          <t>Un pivert</t>
+        </is>
+      </c>
+      <c r="G3" s="52" t="inlineStr">
+        <is>
+          <t>Une horloge</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0:54</t>
+        </is>
+      </c>
+      <c r="C4" s="52" t="inlineStr">
+        <is>
+          <t>Bruit d'humain ou d'animal ?</t>
+        </is>
+      </c>
+      <c r="D4" s="52" t="inlineStr">
+        <is>
+          <t>Un perroquet</t>
+        </is>
+      </c>
+      <c r="E4" s="52" t="inlineStr">
+        <is>
+          <t>Un humain qui râle</t>
+        </is>
+      </c>
+      <c r="F4" s="52" t="inlineStr">
+        <is>
+          <t>Un lutin</t>
+        </is>
+      </c>
+      <c r="G4" s="52" t="inlineStr">
+        <is>
+          <t>Un serpent à sonnette</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1:13</t>
+        </is>
+      </c>
+      <c r="C5" s="52" t="inlineStr">
+        <is>
+          <t>Bruit d'humain ou d'animal ?</t>
+        </is>
+      </c>
+      <c r="D5" s="52" t="inlineStr">
+        <is>
+          <t>Frédéric, 54 ans, qui part en fou rire</t>
+        </is>
+      </c>
+      <c r="E5" s="52" t="inlineStr">
+        <is>
+          <t>Un dindon qui glousse</t>
+        </is>
+      </c>
+      <c r="F5" s="52" t="inlineStr">
+        <is>
+          <t>Un singe</t>
+        </is>
+      </c>
+      <c r="G5" s="52" t="inlineStr">
+        <is>
+          <t>Une personne qui s'esclaffe</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>E06</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0:48</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>EXEMPLE — Que mange-t-elle en priorité dans la nature ?</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Des cerfs</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Des poissons</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Des baies</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1:39</t>
+        </is>
+      </c>
+      <c r="C6" s="52" t="inlineStr">
+        <is>
+          <t>Bruit d'humain ou d'animal ?</t>
+        </is>
+      </c>
+      <c r="D6" s="52" t="inlineStr">
+        <is>
+          <t>Chewbacca</t>
+        </is>
+      </c>
+      <c r="E6" s="52" t="inlineStr">
+        <is>
+          <t>Un rhinocéros</t>
+        </is>
+      </c>
+      <c r="F6" s="52" t="inlineStr">
+        <is>
+          <t>Une personne qui ronfle</t>
+        </is>
+      </c>
+      <c r="G6" s="52" t="inlineStr">
+        <is>
+          <t>Un tigre</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>E06</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1:20</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>EXEMPLE — Combien en reste-t-il à l'état sauvage ?</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Moins de 150</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Environ 3 000</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Plus de 10 000</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2:03</t>
+        </is>
+      </c>
+      <c r="C7" s="52" t="inlineStr">
+        <is>
+          <t>Bruit d'humain ou d'animal ?</t>
+        </is>
+      </c>
+      <c r="D7" s="52" t="inlineStr">
+        <is>
+          <t>Une porte qui grince</t>
+        </is>
+      </c>
+      <c r="E7" s="52" t="inlineStr">
+        <is>
+          <t>Un alligator</t>
+        </is>
+      </c>
+      <c r="F7" s="52" t="inlineStr">
+        <is>
+          <t>Un marteau-piqueur</t>
+        </is>
+      </c>
+      <c r="G7" s="52" t="inlineStr">
+        <is>
+          <t>Une otarie</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2:58</t>
+        </is>
+      </c>
+      <c r="C8" s="52" t="inlineStr">
+        <is>
+          <t>Bruit d'humain ou d'animal ?</t>
+        </is>
+      </c>
+      <c r="D8" s="52" t="inlineStr">
+        <is>
+          <t>C'est de la techno !</t>
+        </is>
+      </c>
+      <c r="E8" s="52" t="inlineStr">
+        <is>
+          <t>Un vautour</t>
+        </is>
+      </c>
+      <c r="F8" s="52" t="inlineStr">
+        <is>
+          <t>Un flamant rose</t>
+        </is>
+      </c>
+      <c r="G8" s="52" t="inlineStr">
+        <is>
+          <t>Un manchot</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3:59</t>
+        </is>
+      </c>
+      <c r="C9" s="52" t="inlineStr">
+        <is>
+          <t>Bruit d'humain ou d'animal ?</t>
+        </is>
+      </c>
+      <c r="D9" s="52" t="inlineStr">
+        <is>
+          <t>Une femme qui crie de détresse</t>
+        </is>
+      </c>
+      <c r="E9" s="52" t="inlineStr">
+        <is>
+          <t>Un renard</t>
+        </is>
+      </c>
+      <c r="F9" s="52" t="inlineStr">
+        <is>
+          <t>Une souricette</t>
+        </is>
+      </c>
+      <c r="G9" s="52" t="inlineStr">
+        <is>
+          <t>Un corbeau</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4:42</t>
+        </is>
+      </c>
+      <c r="C10" s="52" t="inlineStr">
+        <is>
+          <t>Bruit d'humain ou d'animal ?</t>
+        </is>
+      </c>
+      <c r="D10" s="52" t="inlineStr">
+        <is>
+          <t>Un zèbre</t>
+        </is>
+      </c>
+      <c r="E10" s="52" t="inlineStr">
+        <is>
+          <t>Un gecko</t>
+        </is>
+      </c>
+      <c r="F10" s="52" t="inlineStr">
+        <is>
+          <t>Une alarme de voiture de police</t>
+        </is>
+      </c>
+      <c r="G10" s="52" t="inlineStr">
+        <is>
+          <t>Une sonnerie de téléphone</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -3974,7 +3974,7 @@
     <row r="1" ht="58" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>LES QUESTIONS QUI SUIVENT UNE VIDÉO. Une ligne par question. « Apparait a » = la minute de la vidéo où la question s'affiche (écrire 1:13). Le groupe a 10 secondes pour répondre, puis la question se verrouille et montre la bonne réponse. Laisser au moins 13 secondes entre deux questions. Une proposition laissée vide est simplement ignorée.</t>
+          <t>LES QUESTIONS QUI SUIVENT UNE VIDÉO. Une ligne par question. « Apparait a » = la minute de la vidéo où le son commence et où la question s'affiche (écrire 1:13). Le groupe a 13 secondes pour répondre, puis la question se verrouille et nomme la bonne réponse. Laisser au moins 16 secondes entre deux questions, et autant après la dernière. Une proposition laissée vide est simplement ignorée.</t>
         </is>
       </c>
     </row>

--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -1689,7 +1689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1943,132 +1943,132 @@
       <c r="G8" s="12" t="n"/>
     </row>
     <row r="9" ht="30" customFormat="1" customHeight="1" s="39">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>E01</t>
         </is>
       </c>
-      <c r="B9" s="38" t="inlineStr">
+      <c r="B9" s="50" t="inlineStr">
         <is>
           <t>LE COMMISSAIRE JEAN</t>
         </is>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="50" t="inlineStr">
+        <is>
+          <t>les deux</t>
+        </is>
+      </c>
+      <c r="D9" s="50" t="inlineStr">
+        <is>
+          <t>3. Texte ou epreuve</t>
+        </is>
+      </c>
+      <c r="E9" s="50" t="inlineStr">
+        <is>
+          <t>Le coeur de l'etape : le temoignage ecrit, la consigne de l'epreuve, ou l'indice.</t>
+        </is>
+      </c>
+      <c r="F9" s="50" t="inlineStr">
+        <is>
+          <t>Prenez le temps de regarder le panneau d'enquête.</t>
+        </is>
+      </c>
+      <c r="G9" s="50" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customFormat="1" customHeight="1" s="42">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="B10" s="38" t="inlineStr">
+        <is>
+          <t>LE COMMISSAIRE JEAN</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D9" s="37" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E9" s="38" t="inlineStr">
+      <c r="E10" s="38" t="inlineStr">
         <is>
           <t>Afficher la phrase et une photo fournie en arrière plan du texte.</t>
         </is>
       </c>
-      <c r="F9" s="38" t="inlineStr">
+      <c r="F10" s="38" t="inlineStr">
         <is>
           <t>Rendez-vous au bureau des soigneurs pour interroger votre premier témoin.</t>
         </is>
       </c>
-      <c r="G9" s="37" t="n"/>
-    </row>
-    <row r="10" ht="30" customFormat="1" customHeight="1" s="42">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="G10" s="37" t="n"/>
+    </row>
+    <row r="11" ht="30" customFormat="1" customHeight="1" s="36">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>E01</t>
         </is>
       </c>
-      <c r="B10" s="41" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>LE COMMISSAIRE JEAN</t>
         </is>
       </c>
-      <c r="C10" s="40" t="inlineStr">
+      <c r="C11" s="40" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D10" s="40" t="inlineStr">
+      <c r="D11" s="40" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E10" s="41" t="inlineStr">
+      <c r="E11" s="41" t="inlineStr">
         <is>
           <t>Afficher la phrase et une photo fournie en arrière plan du texte.</t>
         </is>
       </c>
-      <c r="F10" s="41" t="inlineStr">
+      <c r="F11" s="41" t="inlineStr">
         <is>
           <t>Rendez-vous au repère sur la carte pour interroger votre premier témoin.</t>
         </is>
       </c>
-      <c r="G10" s="40" t="n"/>
-    </row>
-    <row r="11" ht="30" customFormat="1" customHeight="1" s="36">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="G11" s="40" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>E02</t>
         </is>
       </c>
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>COLLÈGUE SOIGNEUSE</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D11" s="35" t="inlineStr">
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>1. Vidéo de la soigneuse</t>
         </is>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E12" s="35" t="inlineStr">
         <is>
           <t>La vidéo se lance tout de suite après le scan</t>
         </is>
       </c>
-      <c r="F11" s="34" t="n"/>
-      <c r="G11" s="34" t="n"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>E02</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>COLLÈGUE SOIGNEUSE</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>les deux</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>1. Legende du media</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
-        </is>
-      </c>
-      <c r="F12" s="25" t="inlineStr">
-        <is>
-          <t>Mathilde, soigneuse animalière</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="n"/>
+      <c r="F12" s="34" t="n"/>
+      <c r="G12" s="34" t="n"/>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
@@ -2086,150 +2086,150 @@
           <t>les deux</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>1. Legende du media</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="inlineStr">
+        <is>
+          <t>Mathilde, soigneuse animalière</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="n"/>
+    </row>
+    <row r="14" ht="30" customFormat="1" customHeight="1" s="39">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>COLLÈGUE SOIGNEUSE</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>les deux</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>3. Texte ou epreuve</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Le coeur de l'etape : le temoignage ecrit, la consigne de l'epreuve, ou l'indice. Aussi long que necessaire.</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Vous êtes dans le bureau des soigneurs, le dernier lieu où a été aperçue Isabelle. Prenez le temps d'observer la scène et prenez des notes si nécessaire. </t>
         </is>
       </c>
-      <c r="G13" s="12" t="n"/>
-    </row>
-    <row r="14" ht="30" customFormat="1" customHeight="1" s="39">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="G14" s="12" t="n"/>
+    </row>
+    <row r="15" ht="30" customFormat="1" customHeight="1" s="42">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>E02</t>
         </is>
       </c>
-      <c r="B14" s="38" t="inlineStr">
+      <c r="B15" s="38" t="inlineStr">
         <is>
           <t>COLLÈGUE SOIGNEUSE</t>
         </is>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D14" s="37" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E14" s="37" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS A. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F14" s="37" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Rendez-vous à l'aire de pique-nique en face des ours polaires pour observer les caméras de surveillance du Parc.</t>
         </is>
       </c>
-      <c r="G14" s="37" t="n"/>
-    </row>
-    <row r="15" ht="30" customFormat="1" customHeight="1" s="42">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="G15" s="37" t="n"/>
+    </row>
+    <row r="16" ht="30" customFormat="1" customHeight="1" s="36">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>E02</t>
         </is>
       </c>
-      <c r="B15" s="41" t="inlineStr">
+      <c r="B16" s="41" t="inlineStr">
         <is>
           <t>COLLÈGUE SOIGNEUSE</t>
         </is>
       </c>
-      <c r="C15" s="40" t="inlineStr">
+      <c r="C16" s="40" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D15" s="40" t="inlineStr">
+      <c r="D16" s="40" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E15" s="40" t="inlineStr">
+      <c r="E16" s="40" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B.</t>
         </is>
       </c>
-      <c r="F15" s="40" t="inlineStr">
+      <c r="F16" s="40" t="inlineStr">
         <is>
           <t>Rendez-vous au niveau de l'enclos des loups pour la suite de l'enquête</t>
         </is>
       </c>
-      <c r="G15" s="40" t="n"/>
-    </row>
-    <row r="16" ht="30" customFormat="1" customHeight="1" s="36">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="G16" s="40" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>E03</t>
         </is>
       </c>
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>SOPHIE, CHEFFE DE LA SÉCURITÉ</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D16" s="35" t="inlineStr">
+      <c r="D17" s="35" t="inlineStr">
         <is>
           <t>1. Vidéo de Sophie</t>
         </is>
       </c>
-      <c r="E16" s="35" t="inlineStr">
+      <c r="E17" s="35" t="inlineStr">
         <is>
           <t>La vidéo se lance tout de suite après le scan</t>
         </is>
       </c>
-      <c r="F16" s="34" t="n"/>
-      <c r="G16" s="34" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>SOPHIE, CHEFFE DE LA SÉCURITÉ</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>les deux</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>2. Legende du media</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
-        </is>
-      </c>
-      <c r="F17" s="25" t="inlineStr">
-        <is>
-          <t>Sophie, cheffe de la sécurité</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="n"/>
+      <c r="F17" s="34" t="n"/>
+      <c r="G17" s="34" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
@@ -2249,606 +2249,606 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
+          <t>2. Legende du media</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
+        </is>
+      </c>
+      <c r="F18" s="25" t="inlineStr">
+        <is>
+          <t>Sophie, cheffe de la sécurité</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="30" customFormat="1" customHeight="1" s="39">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>SOPHIE, CHEFFE DE LA SÉCURITÉ</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>les deux</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
           <t>3. Texte ou epreuve</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Le coeur de l'etape : le temoignage ecrit, la consigne de l'epreuve, ou l'indice. Aussi long que necessaire.</t>
         </is>
       </c>
-      <c r="F18" s="25" t="inlineStr">
+      <c r="F19" s="25" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="G18" s="12" t="n"/>
-    </row>
-    <row r="19" ht="30" customFormat="1" customHeight="1" s="39">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="G19" s="12" t="n"/>
+    </row>
+    <row r="20" ht="30" customFormat="1" customHeight="1" s="44">
+      <c r="A20" s="37" t="inlineStr">
         <is>
           <t>E03</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>SOPHIE, CHEFFE DE LA SÉCURITÉ</t>
         </is>
       </c>
-      <c r="C19" s="37" t="inlineStr">
+      <c r="C20" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D19" s="37" t="inlineStr">
+      <c r="D20" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E19" s="37" t="inlineStr">
+      <c r="E20" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS A. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F19" s="37" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>Rendez-vous au niveau de l'enclos des loups pour la suite de l'enquête</t>
         </is>
       </c>
-      <c r="G19" s="37" t="n"/>
-    </row>
-    <row r="20" ht="30" customFormat="1" customHeight="1" s="44">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="G20" s="37" t="n"/>
+    </row>
+    <row r="21" ht="44" customFormat="1" customHeight="1" s="36">
+      <c r="A21" s="43" t="inlineStr">
         <is>
           <t>E03</t>
         </is>
       </c>
-      <c r="B20" s="43" t="inlineStr">
+      <c r="B21" s="43" t="inlineStr">
         <is>
           <t>SOPHIE, CHEFFE DE LA SÉCURITÉ</t>
         </is>
       </c>
-      <c r="C20" s="43" t="inlineStr">
+      <c r="C21" s="43" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D20" s="43" t="inlineStr">
+      <c r="D21" s="43" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E20" s="43" t="inlineStr">
+      <c r="E21" s="43" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B.</t>
         </is>
       </c>
-      <c r="F20" s="45" t="inlineStr">
+      <c r="F21" s="45" t="inlineStr">
         <is>
           <t>Rendez-vous au point GPS pour interroger votre prochain témoin.</t>
         </is>
       </c>
-      <c r="G20" s="43" t="n"/>
-    </row>
-    <row r="21" ht="44" customFormat="1" customHeight="1" s="36">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="G21" s="43" t="n"/>
+    </row>
+    <row r="22" ht="30" customFormat="1" customHeight="1" s="39">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>E04</t>
         </is>
       </c>
-      <c r="B21" s="34" t="inlineStr">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>L'ENCLOS DES LOUPS</t>
         </is>
       </c>
-      <c r="C21" s="34" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D21" s="34" t="inlineStr">
+      <c r="D22" s="34" t="inlineStr">
         <is>
           <t>1. Accueil apres le scan</t>
         </is>
       </c>
-      <c r="E21" s="34" t="inlineStr">
+      <c r="E22" s="34" t="inlineStr">
         <is>
           <t>La phrase d'accroche affichee juste apres le scan, au-dessus du bouton. Une ou deux lignes, pas plus : le groupe est debout, il n'a pas envie de lire.</t>
         </is>
       </c>
-      <c r="F21" s="34" t="inlineStr">
+      <c r="F22" s="34" t="inlineStr">
         <is>
           <t>Observez l'enclos à l'aide des jumelles à la recherche d'un objet qui n'est pas à sa place. Vous trouverez un indice sur cet objet, à noter soigneusement.</t>
         </is>
       </c>
-      <c r="G21" s="34" t="n"/>
-    </row>
-    <row r="22" ht="30" customFormat="1" customHeight="1" s="39">
-      <c r="A22" s="37" t="inlineStr">
+      <c r="G22" s="34" t="n"/>
+    </row>
+    <row r="23" ht="30" customFormat="1" customHeight="1" s="44">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>E04</t>
         </is>
       </c>
-      <c r="B22" s="37" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>L'ENCLOS DES LOUPS</t>
         </is>
       </c>
-      <c r="C22" s="37" t="inlineStr">
+      <c r="C23" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D22" s="37" t="inlineStr">
+      <c r="D23" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E22" s="37" t="inlineStr">
+      <c r="E23" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS A. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F22" s="38" t="inlineStr">
+      <c r="F23" s="38" t="inlineStr">
         <is>
           <t>Rendez-vous au-dessus de l'enclos des loups pour interroger votre prochain témoin</t>
         </is>
       </c>
-      <c r="G22" s="37" t="n"/>
-    </row>
-    <row r="23" ht="30" customFormat="1" customHeight="1" s="44">
-      <c r="A23" s="43" t="inlineStr">
+      <c r="G23" s="37" t="n"/>
+    </row>
+    <row r="24" ht="30" customFormat="1" customHeight="1" s="36">
+      <c r="A24" s="43" t="inlineStr">
         <is>
           <t>E04</t>
         </is>
       </c>
-      <c r="B23" s="43" t="inlineStr">
+      <c r="B24" s="43" t="inlineStr">
         <is>
           <t>L'ENCLOS DES LOUPS</t>
         </is>
       </c>
-      <c r="C23" s="43" t="inlineStr">
+      <c r="C24" s="43" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D23" s="43" t="inlineStr">
+      <c r="D24" s="43" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E23" s="43" t="inlineStr">
+      <c r="E24" s="43" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B.</t>
         </is>
       </c>
-      <c r="F23" s="45" t="inlineStr">
+      <c r="F24" s="45" t="inlineStr">
         <is>
           <t>Rendez-vous au-dessus de l'enclos des loups pour interroger votre prochain témoin</t>
         </is>
       </c>
-      <c r="G23" s="43" t="n"/>
-    </row>
-    <row r="24" ht="30" customFormat="1" customHeight="1" s="36">
-      <c r="A24" s="35" t="inlineStr">
+      <c r="G24" s="43" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>E05</t>
         </is>
       </c>
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>LA PASSANTE</t>
         </is>
       </c>
-      <c r="C24" s="34" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D24" s="35" t="inlineStr">
+      <c r="D25" s="35" t="inlineStr">
         <is>
           <t>1. Vidéo de la passante</t>
         </is>
       </c>
-      <c r="E24" s="35" t="inlineStr">
+      <c r="E25" s="35" t="inlineStr">
         <is>
           <t>La vidéo se lance tout de suite après le scan</t>
         </is>
       </c>
-      <c r="F24" s="34" t="n"/>
-      <c r="G24" s="34" t="n"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="F25" s="34" t="n"/>
+      <c r="G25" s="34" t="n"/>
+    </row>
+    <row r="26" ht="30" customFormat="1" customHeight="1" s="39">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>E05</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>LA PASSANTE</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>2. Legende du media</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
         </is>
       </c>
-      <c r="F25" s="25" t="inlineStr">
+      <c r="F26" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Marina, passait juste par là </t>
         </is>
       </c>
-      <c r="G25" s="12" t="n"/>
-    </row>
-    <row r="26" ht="30" customFormat="1" customHeight="1" s="39">
-      <c r="A26" s="38" t="inlineStr">
+      <c r="G26" s="12" t="n"/>
+    </row>
+    <row r="27" ht="30" customFormat="1" customHeight="1" s="44">
+      <c r="A27" s="38" t="inlineStr">
         <is>
           <t>E05</t>
         </is>
       </c>
-      <c r="B26" s="38" t="inlineStr">
+      <c r="B27" s="38" t="inlineStr">
         <is>
           <t>LA PASSANTE</t>
         </is>
       </c>
-      <c r="C26" s="37" t="inlineStr">
+      <c r="C27" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D26" s="37" t="inlineStr">
+      <c r="D27" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E26" s="37" t="inlineStr">
+      <c r="E27" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS A. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F26" s="38" t="inlineStr">
+      <c r="F27" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">Rendez-vous devant la panthère de l'amour pour un quiz animalier </t>
         </is>
       </c>
-      <c r="G26" s="37" t="n"/>
-    </row>
-    <row r="27" ht="30" customFormat="1" customHeight="1" s="44">
-      <c r="A27" s="45" t="inlineStr">
+      <c r="G27" s="37" t="n"/>
+    </row>
+    <row r="28" ht="30" customFormat="1" customHeight="1" s="36">
+      <c r="A28" s="45" t="inlineStr">
         <is>
           <t>E05</t>
         </is>
       </c>
-      <c r="B27" s="45" t="inlineStr">
+      <c r="B28" s="45" t="inlineStr">
         <is>
           <t>LA PASSANTE</t>
         </is>
       </c>
-      <c r="C27" s="43" t="inlineStr">
+      <c r="C28" s="43" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D27" s="43" t="inlineStr">
+      <c r="D28" s="43" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E27" s="43" t="inlineStr">
+      <c r="E28" s="43" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B.</t>
         </is>
       </c>
-      <c r="F27" s="45" t="inlineStr">
+      <c r="F28" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Rendez-vous devant la panthère de l'amour pour un quiz animalier </t>
         </is>
       </c>
-      <c r="G27" s="43" t="n"/>
-    </row>
-    <row r="28" ht="30" customFormat="1" customHeight="1" s="36">
-      <c r="A28" s="35" t="inlineStr">
+      <c r="G28" s="43" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>E06</t>
         </is>
       </c>
-      <c r="B28" s="35" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>QUIZ ANIMALIER</t>
         </is>
       </c>
-      <c r="C28" s="34" t="inlineStr">
+      <c r="C29" s="34" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D28" s="35" t="inlineStr">
+      <c r="D29" s="35" t="inlineStr">
         <is>
           <t>1. Vidéo n°1 Sabri et Arez</t>
         </is>
       </c>
-      <c r="E28" s="35" t="inlineStr">
+      <c r="E29" s="35" t="inlineStr">
         <is>
           <t>La vidéo se lance tout de suite après le scan</t>
         </is>
       </c>
-      <c r="F28" s="34" t="n"/>
-      <c r="G28" s="34" t="n"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="46" t="inlineStr">
+      <c r="F29" s="34" t="n"/>
+      <c r="G29" s="34" t="n"/>
+    </row>
+    <row r="30" ht="30" customFormat="1" customHeight="1" s="39">
+      <c r="A30" s="46" t="inlineStr">
         <is>
           <t>E06</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>QUIZ ANIMALIER</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>3. Texte ou epreuve</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Le coeur de l'etape : le temoignage ecrit, la consigne de l'epreuve, ou l'indice. Aussi long que necessaire.</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>Le quiz s'affiche sous la video de l'ecran 1. Les questions sont dans l'onglet Quiz.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customFormat="1" customHeight="1" s="39">
-      <c r="A30" s="38" t="inlineStr">
+    <row r="31" ht="30" customFormat="1" customHeight="1" s="44">
+      <c r="A31" s="38" t="inlineStr">
         <is>
           <t>E06</t>
         </is>
       </c>
-      <c r="B30" s="38" t="inlineStr">
+      <c r="B31" s="38" t="inlineStr">
         <is>
           <t>QUIZ ANIMALIER</t>
         </is>
       </c>
-      <c r="C30" s="37" t="inlineStr">
+      <c r="C31" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D30" s="37" t="inlineStr">
+      <c r="D31" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E30" s="37" t="inlineStr">
+      <c r="E31" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS A. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F30" s="38" t="inlineStr">
+      <c r="F31" s="38" t="inlineStr">
         <is>
           <t>Enfoncez-vous dans la forêt pour la suite de l'enquête</t>
         </is>
       </c>
-      <c r="G30" s="37" t="n"/>
-    </row>
-    <row r="31" ht="30" customFormat="1" customHeight="1" s="44">
-      <c r="A31" s="45" t="inlineStr">
+      <c r="G31" s="37" t="n"/>
+    </row>
+    <row r="32" ht="30" customFormat="1" customHeight="1" s="36">
+      <c r="A32" s="45" t="inlineStr">
         <is>
           <t>E06</t>
         </is>
       </c>
-      <c r="B31" s="45" t="inlineStr">
+      <c r="B32" s="45" t="inlineStr">
         <is>
           <t>QUIZ ANIMALIER</t>
         </is>
       </c>
-      <c r="C31" s="43" t="inlineStr">
+      <c r="C32" s="43" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D31" s="43" t="inlineStr">
+      <c r="D32" s="43" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E31" s="43" t="inlineStr">
+      <c r="E32" s="43" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B.</t>
         </is>
       </c>
-      <c r="F31" s="45" t="inlineStr">
+      <c r="F32" s="45" t="inlineStr">
         <is>
           <t>Enfoncez-vous dans la forêt pour la suite de l'enquête</t>
         </is>
       </c>
-      <c r="G31" s="43" t="n"/>
-    </row>
-    <row r="32" ht="30" customFormat="1" customHeight="1" s="36">
-      <c r="A32" s="35" t="inlineStr">
+      <c r="G32" s="43" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="35" t="inlineStr">
         <is>
           <t>E07</t>
         </is>
       </c>
-      <c r="B32" s="35" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>VÉTÉRINAIRE</t>
         </is>
       </c>
-      <c r="C32" s="34" t="inlineStr">
+      <c r="C33" s="34" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D32" s="35" t="inlineStr">
+      <c r="D33" s="35" t="inlineStr">
         <is>
           <t>1. Vidéo de Sandra</t>
         </is>
       </c>
-      <c r="E32" s="35" t="inlineStr">
+      <c r="E33" s="35" t="inlineStr">
         <is>
           <t>La vidéo se lance tout de suite après le scan</t>
         </is>
       </c>
-      <c r="F32" s="34" t="n"/>
-      <c r="G32" s="34" t="n"/>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="F33" s="34" t="n"/>
+      <c r="G33" s="34" t="n"/>
+    </row>
+    <row r="34" ht="30" customFormat="1" customHeight="1" s="39">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>E07</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>VÉTÉRINAIRE</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>2. Legende du media</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
         </is>
       </c>
-      <c r="F33" s="25" t="inlineStr">
+      <c r="F34" s="25" t="inlineStr">
         <is>
           <t>Sandra, Vétérinaire au Parc Zoologique et Botanique de Mulhouse</t>
         </is>
       </c>
-      <c r="G33" s="12" t="n"/>
-    </row>
-    <row r="34" ht="30" customFormat="1" customHeight="1" s="39">
-      <c r="A34" s="38" t="inlineStr">
+      <c r="G34" s="12" t="n"/>
+    </row>
+    <row r="35" ht="30" customFormat="1" customHeight="1" s="44">
+      <c r="A35" s="38" t="inlineStr">
         <is>
           <t>E07</t>
         </is>
       </c>
-      <c r="B34" s="38" t="inlineStr">
+      <c r="B35" s="38" t="inlineStr">
         <is>
           <t>VÉTÉRINAIRE</t>
         </is>
       </c>
-      <c r="C34" s="37" t="inlineStr">
+      <c r="C35" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D34" s="37" t="inlineStr">
+      <c r="D35" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
+      <c r="E35" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS A. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F34" s="38" t="inlineStr">
+      <c r="F35" s="38" t="inlineStr">
         <is>
           <t>Tableau des empreintes</t>
         </is>
       </c>
-      <c r="G34" s="37" t="n"/>
-    </row>
-    <row r="35" ht="30" customFormat="1" customHeight="1" s="44">
-      <c r="A35" s="45" t="inlineStr">
+      <c r="G35" s="37" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="45" t="inlineStr">
         <is>
           <t>E07</t>
         </is>
       </c>
-      <c r="B35" s="45" t="inlineStr">
+      <c r="B36" s="45" t="inlineStr">
         <is>
           <t>VÉTÉRINAIRE</t>
         </is>
       </c>
-      <c r="C35" s="43" t="inlineStr">
+      <c r="C36" s="43" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D35" s="43" t="inlineStr">
+      <c r="D36" s="43" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E35" s="43" t="inlineStr">
+      <c r="E36" s="43" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B.</t>
         </is>
       </c>
-      <c r="F35" s="45" t="inlineStr">
+      <c r="F36" s="45" t="inlineStr">
         <is>
           <t>Tableau des empreintes</t>
         </is>
       </c>
-      <c r="G35" s="43" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>E08</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>Indice : le panneau d'empreinte</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>les deux</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>1. Accueil apres le scan</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>La phrase d'accroche affichee juste apres le scan, au-dessus du bouton. Une ou deux lignes, pas plus : le groupe est debout, il n'a pas envie de lire.</t>
-        </is>
-      </c>
-      <c r="F36" s="25" t="inlineStr">
-        <is>
-          <t>Vous l'aurez compris, un animal a semé la zizanie dans le parc hier soir. Saurez-vous l'identifier sur ce panneau ?</t>
-        </is>
-      </c>
-      <c r="G36" s="12" t="n"/>
+      <c r="G36" s="43" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="14" t="inlineStr">
@@ -2868,449 +2868,445 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
+          <t>1. Accueil apres le scan</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>La phrase d'accroche affichee juste apres le scan, au-dessus du bouton. Une ou deux lignes, pas plus : le groupe est debout, il n'a pas envie de lire.</t>
+        </is>
+      </c>
+      <c r="F37" s="25" t="inlineStr">
+        <is>
+          <t>Vous l'aurez compris, un animal a semé la zizanie dans le parc hier soir. Saurez-vous l'identifier sur ce panneau ?</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="n"/>
+    </row>
+    <row r="38" ht="30" customFormat="1" customHeight="1" s="39">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>E08</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Indice : le panneau d'empreinte</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>les deux</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
           <t>3. Texte ou epreuve</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Le coeur de l'etape : le temoignage ecrit, la consigne de l'epreuve, ou l'indice. Aussi long que necessaire.</t>
         </is>
       </c>
-      <c r="F37" s="25" t="inlineStr">
+      <c r="F38" s="25" t="inlineStr">
         <is>
           <t>Quel est le numéro de l'animal qui était présent dans le zoo hier soir ?</t>
         </is>
       </c>
-      <c r="G37" s="25" t="inlineStr">
+      <c r="G38" s="25" t="inlineStr">
         <is>
           <t>créer un champ libre, bonne réponse = 11. SI 11, donner l'indice "S"</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="30" customFormat="1" customHeight="1" s="39">
-      <c r="A38" s="38" t="inlineStr">
+    <row r="39" ht="30" customFormat="1" customHeight="1" s="44">
+      <c r="A39" s="38" t="inlineStr">
         <is>
           <t>E08</t>
         </is>
       </c>
-      <c r="B38" s="37" t="inlineStr">
+      <c r="B39" s="37" t="inlineStr">
         <is>
           <t>Indice : le panneau d'empreinte</t>
         </is>
       </c>
-      <c r="C38" s="37" t="inlineStr">
+      <c r="C39" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D38" s="37" t="inlineStr">
+      <c r="D39" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E38" s="37" t="inlineStr">
+      <c r="E39" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS A. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F38" s="38" t="inlineStr">
+      <c r="F39" s="38" t="inlineStr">
         <is>
           <t>Rendez-vous au point GPS pour interroger votre prochain témoin.</t>
         </is>
       </c>
-      <c r="G38" s="37" t="n"/>
-    </row>
-    <row r="39" ht="30" customFormat="1" customHeight="1" s="44">
-      <c r="A39" s="45" t="inlineStr">
+      <c r="G39" s="37" t="n"/>
+    </row>
+    <row r="40" ht="30" customFormat="1" customHeight="1" s="36">
+      <c r="A40" s="45" t="inlineStr">
         <is>
           <t>E08</t>
         </is>
       </c>
-      <c r="B39" s="43" t="inlineStr">
+      <c r="B40" s="43" t="inlineStr">
         <is>
           <t>Indice : le panneau d'empreinte</t>
         </is>
       </c>
-      <c r="C39" s="43" t="inlineStr">
+      <c r="C40" s="43" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D39" s="43" t="inlineStr">
+      <c r="D40" s="43" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E39" s="43" t="inlineStr">
+      <c r="E40" s="43" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B.</t>
         </is>
       </c>
-      <c r="F39" s="45" t="inlineStr">
+      <c r="F40" s="45" t="inlineStr">
         <is>
           <t>Vous avez désormais intérrogé tous les témoins officiels. Analysez les 4 lettres que vous avez trouvé pour continuer votre enquête.</t>
         </is>
       </c>
-      <c r="G39" s="43" t="n"/>
-    </row>
-    <row r="40" ht="30" customFormat="1" customHeight="1" s="36">
-      <c r="A40" s="35" t="inlineStr">
+      <c r="G40" s="43" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
         <is>
           <t>E09</t>
         </is>
       </c>
-      <c r="B40" s="34" t="inlineStr">
+      <c r="B41" s="34" t="inlineStr">
         <is>
           <t>Greg, version sens A</t>
         </is>
       </c>
-      <c r="C40" s="34" t="inlineStr">
+      <c r="C41" s="34" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D40" s="35" t="inlineStr">
+      <c r="D41" s="35" t="inlineStr">
         <is>
           <t>1. Vidéo de Greg</t>
         </is>
       </c>
-      <c r="E40" s="35" t="inlineStr">
+      <c r="E41" s="35" t="inlineStr">
         <is>
           <t>La vidéo se lance tout de suite après le scan</t>
         </is>
       </c>
-      <c r="F40" s="34" t="n"/>
-      <c r="G40" s="34" t="n"/>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="F41" s="34" t="n"/>
+      <c r="G41" s="34" t="n"/>
+    </row>
+    <row r="42" ht="30" customFormat="1" customHeight="1" s="39">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>E09</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>Greg, version sens A</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>2. Legende du media</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
         </is>
       </c>
-      <c r="F41" s="25" t="inlineStr">
+      <c r="F42" s="25" t="inlineStr">
         <is>
           <t>Greg, pas très rassurant</t>
         </is>
       </c>
-      <c r="G41" s="12" t="n"/>
-    </row>
-    <row r="42" ht="30" customFormat="1" customHeight="1" s="39">
-      <c r="A42" s="38" t="inlineStr">
+      <c r="G42" s="12" t="n"/>
+    </row>
+    <row r="43" ht="30" customFormat="1" customHeight="1" s="36">
+      <c r="A43" s="38" t="inlineStr">
         <is>
           <t>E09</t>
         </is>
       </c>
-      <c r="B42" s="37" t="inlineStr">
+      <c r="B43" s="37" t="inlineStr">
         <is>
           <t>Greg, version sens A</t>
         </is>
       </c>
-      <c r="C42" s="37" t="inlineStr">
+      <c r="C43" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D42" s="37" t="inlineStr">
+      <c r="D43" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E42" s="37" t="inlineStr">
+      <c r="E43" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS A. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F42" s="38" t="inlineStr">
+      <c r="F43" s="38" t="inlineStr">
         <is>
           <t>Rendez-vous dans la grande volière pour interroger Bill.</t>
         </is>
       </c>
-      <c r="G42" s="37" t="n"/>
-    </row>
-    <row r="43" ht="30" customFormat="1" customHeight="1" s="36">
-      <c r="A43" s="35" t="inlineStr">
+      <c r="G43" s="37" t="n"/>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="35" t="inlineStr">
         <is>
           <t>E10</t>
         </is>
       </c>
-      <c r="B43" s="34" t="inlineStr">
+      <c r="B44" s="34" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="C43" s="34" t="inlineStr">
+      <c r="C44" s="34" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D43" s="35" t="inlineStr">
+      <c r="D44" s="35" t="inlineStr">
         <is>
           <t>1. Vidéo de Bill</t>
         </is>
       </c>
-      <c r="E43" s="35" t="inlineStr">
+      <c r="E44" s="35" t="inlineStr">
         <is>
           <t>La vidéo se lance tout de suite après le scan</t>
         </is>
       </c>
-      <c r="F43" s="34" t="n"/>
-      <c r="G43" s="34" t="n"/>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="14" t="inlineStr">
+      <c r="F44" s="34" t="n"/>
+      <c r="G44" s="34" t="n"/>
+    </row>
+    <row r="45" ht="30" customFormat="1" customHeight="1" s="39">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>E10</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>2. Legende du media</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
         </is>
       </c>
-      <c r="F44" s="25" t="inlineStr">
+      <c r="F45" s="25" t="inlineStr">
         <is>
           <t>Bill, passionné d'oiseaux</t>
         </is>
       </c>
-      <c r="G44" s="12" t="n"/>
-    </row>
-    <row r="45" ht="30" customFormat="1" customHeight="1" s="39">
-      <c r="A45" s="38" t="inlineStr">
+      <c r="G45" s="12" t="n"/>
+    </row>
+    <row r="46" ht="30" customFormat="1" customHeight="1" s="44">
+      <c r="A46" s="38" t="inlineStr">
         <is>
           <t>E10</t>
         </is>
       </c>
-      <c r="B45" s="37" t="inlineStr">
+      <c r="B46" s="37" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="C45" s="37" t="inlineStr">
+      <c r="C46" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D45" s="37" t="inlineStr">
+      <c r="D46" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E45" s="38" t="inlineStr">
+      <c r="E46" s="38" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS A. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F45" s="38" t="inlineStr">
+      <c r="F46" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">Avant d'aller vérifier le bureau de Greg, rendez-vous au point GPS </t>
         </is>
       </c>
-      <c r="G45" s="37" t="n"/>
-    </row>
-    <row r="46" ht="30" customFormat="1" customHeight="1" s="44">
-      <c r="A46" s="45" t="inlineStr">
+      <c r="G46" s="37" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="45" t="inlineStr">
         <is>
           <t>E10</t>
         </is>
       </c>
-      <c r="B46" s="43" t="inlineStr">
+      <c r="B47" s="43" t="inlineStr">
         <is>
           <t>Bill</t>
         </is>
       </c>
-      <c r="C46" s="43" t="inlineStr">
+      <c r="C47" s="43" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D46" s="43" t="inlineStr">
+      <c r="D47" s="43" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E46" s="43" t="inlineStr">
+      <c r="E47" s="43" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B.</t>
         </is>
       </c>
-      <c r="F46" s="45" t="inlineStr">
+      <c r="F47" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">Avant d'aller vérifier le bureau de Greg, rendez-vous au point GPS </t>
         </is>
       </c>
-      <c r="G46" s="43" t="n"/>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="14" t="inlineStr">
+      <c r="G47" s="43" t="n"/>
+    </row>
+    <row r="48" ht="30" customFormat="1" customHeight="1" s="39">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>E11</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>Indice : Le sac du botaniste</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D47" s="11" t="inlineStr">
+      <c r="D48" s="11" t="inlineStr">
         <is>
           <t>1. Accueil apres le scan</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>La phrase d'accroche affichee juste apres le scan, au-dessus du bouton. Une ou deux lignes, pas plus : le groupe est debout, il n'a pas envie de lire.</t>
         </is>
       </c>
-      <c r="F47" s="12" t="inlineStr">
+      <c r="F48" s="12" t="inlineStr">
         <is>
           <t>Qu'est-ce que c'est que ce sac ? Observez bien son contenu.</t>
         </is>
       </c>
-      <c r="G47" s="12" t="n"/>
-    </row>
-    <row r="48" ht="30" customFormat="1" customHeight="1" s="39">
-      <c r="A48" s="38" t="inlineStr">
+      <c r="G48" s="12" t="n"/>
+    </row>
+    <row r="49" ht="30" customFormat="1" customHeight="1" s="44">
+      <c r="A49" s="38" t="inlineStr">
         <is>
           <t>E11</t>
         </is>
       </c>
-      <c r="B48" s="37" t="inlineStr">
+      <c r="B49" s="37" t="inlineStr">
         <is>
           <t>Indice : Le sac du botaniste</t>
         </is>
       </c>
-      <c r="C48" s="37" t="inlineStr">
+      <c r="C49" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D48" s="37" t="inlineStr">
+      <c r="D49" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E48" s="37" t="inlineStr">
+      <c r="E49" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS A. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F48" s="37" t="inlineStr">
+      <c r="F49" s="37" t="inlineStr">
         <is>
           <t>Suivez le chemin indiqué pour poursuivre l'enquête</t>
         </is>
       </c>
-      <c r="G48" s="37" t="n"/>
-    </row>
-    <row r="49" ht="30" customFormat="1" customHeight="1" s="44">
-      <c r="A49" s="45" t="inlineStr">
+      <c r="G49" s="37" t="n"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="45" t="inlineStr">
         <is>
           <t>E11</t>
         </is>
       </c>
-      <c r="B49" s="43" t="inlineStr">
+      <c r="B50" s="43" t="inlineStr">
         <is>
           <t>Indice : Le sac du botaniste</t>
         </is>
       </c>
-      <c r="C49" s="43" t="inlineStr">
+      <c r="C50" s="43" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D49" s="43" t="inlineStr">
+      <c r="D50" s="43" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E49" s="43" t="inlineStr">
+      <c r="E50" s="43" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B.</t>
         </is>
       </c>
-      <c r="F49" s="43" t="inlineStr">
+      <c r="F50" s="43" t="inlineStr">
         <is>
           <t>Suivez le chemin indiqué pour poursuivre l'enquête</t>
         </is>
       </c>
-      <c r="G49" s="43" t="n"/>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="inlineStr">
-        <is>
-          <t>Appel du commissaire</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>les deux</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>1. Accueil apres le scan</t>
-        </is>
-      </c>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>La phrase d'accroche affichee juste apres le scan, au-dessus du bouton. Une ou deux lignes, pas plus : le groupe est debout, il n'a pas envie de lire.</t>
-        </is>
-      </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>Vous avez un appel entrant du Commissaire Jean</t>
-        </is>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>sonnerie émise, il faudrait que les gens puisse toucher le bouton "décrocher pour déclencher l'audio"</t>
-        </is>
-      </c>
+      <c r="G50" s="43" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
@@ -3330,20 +3326,24 @@
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>2. Legende du media</t>
+          <t>1. Accueil apres le scan</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
+          <t>La phrase d'accroche affichee juste apres le scan, au-dessus du bouton. Une ou deux lignes, pas plus : le groupe est debout, il n'a pas envie de lire.</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>Commissaire Jean, dubitatif</t>
-        </is>
-      </c>
-      <c r="G51" s="12" t="n"/>
+          <t>Vous avez un appel entrant du Commissaire Jean</t>
+        </is>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>sonnerie émise, il faudrait que les gens puisse toucher le bouton "décrocher pour déclencher l'audio"</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
@@ -3363,255 +3363,255 @@
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
+          <t>2. Legende du media</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>Commissaire Jean, dubitatif</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="n"/>
+    </row>
+    <row r="53" ht="30" customFormat="1" customHeight="1" s="39">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>E12</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>Appel du commissaire</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>les deux</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
           <t>3. Texte ou epreuve</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>Le coeur de l'etape : le temoignage ecrit, la consigne de l'epreuve, ou l'indice. Aussi long que necessaire.</t>
         </is>
       </c>
-      <c r="F52" s="12" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="G52" s="12" t="inlineStr">
+      <c r="G53" s="12" t="inlineStr">
         <is>
           <t>Fichier audio</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customFormat="1" customHeight="1" s="39">
-      <c r="A53" s="37" t="inlineStr">
+    <row r="54" ht="30" customFormat="1" customHeight="1" s="44">
+      <c r="A54" s="37" t="inlineStr">
         <is>
           <t>E12</t>
         </is>
       </c>
-      <c r="B53" s="37" t="inlineStr">
+      <c r="B54" s="37" t="inlineStr">
         <is>
           <t>Appel du commissaire</t>
         </is>
       </c>
-      <c r="C53" s="37" t="inlineStr">
+      <c r="C54" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D53" s="37" t="inlineStr">
+      <c r="D54" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E53" s="37" t="inlineStr">
+      <c r="E54" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS A. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F53" s="37" t="inlineStr">
+      <c r="F54" s="37" t="inlineStr">
         <is>
           <t>Poursuivez jusqu'au bureau de Greg</t>
         </is>
       </c>
-      <c r="G53" s="37" t="n"/>
-    </row>
-    <row r="54" ht="30" customFormat="1" customHeight="1" s="44">
-      <c r="A54" s="43" t="inlineStr">
+      <c r="G54" s="37" t="n"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="43" t="inlineStr">
         <is>
           <t>E12</t>
         </is>
       </c>
-      <c r="B54" s="43" t="inlineStr">
+      <c r="B55" s="43" t="inlineStr">
         <is>
           <t>Appel du commissaire</t>
         </is>
       </c>
-      <c r="C54" s="43" t="inlineStr">
+      <c r="C55" s="43" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D54" s="43" t="inlineStr">
+      <c r="D55" s="43" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E54" s="43" t="inlineStr">
+      <c r="E55" s="43" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B.</t>
         </is>
       </c>
-      <c r="F54" s="43" t="inlineStr">
+      <c r="F55" s="43" t="inlineStr">
         <is>
           <t>Poursuivez jusqu'au bureau de Greg</t>
         </is>
       </c>
-      <c r="G54" s="43" t="n"/>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
+      <c r="G55" s="43" t="n"/>
+    </row>
+    <row r="56" ht="30" customFormat="1" customHeight="1" s="39">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>E13</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>Bureau de Greg</t>
         </is>
       </c>
-      <c r="C55" s="11" t="inlineStr">
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D55" s="11" t="inlineStr">
+      <c r="D56" s="11" t="inlineStr">
         <is>
           <t>1. Accueil apres le scan</t>
         </is>
       </c>
-      <c r="E55" s="11" t="inlineStr">
+      <c r="E56" s="11" t="inlineStr">
         <is>
           <t>La phrase d'accroche affichee juste apres le scan, au-dessus du bouton. Une ou deux lignes, pas plus : le groupe est debout, il n'a pas envie de lire.</t>
         </is>
       </c>
-      <c r="F55" s="12" t="inlineStr">
+      <c r="F56" s="12" t="inlineStr">
         <is>
           <t>Observez le bureau de Greg à la recherche d'indices</t>
         </is>
       </c>
-      <c r="G55" s="12" t="inlineStr">
+      <c r="G56" s="12" t="inlineStr">
         <is>
           <t>ils trouvent un indice supplémentaire</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="30" customFormat="1" customHeight="1" s="39">
-      <c r="A56" s="37" t="inlineStr">
+    <row r="57" ht="30" customFormat="1" customHeight="1" s="44">
+      <c r="A57" s="37" t="inlineStr">
         <is>
           <t>E13</t>
         </is>
       </c>
-      <c r="B56" s="37" t="inlineStr">
+      <c r="B57" s="37" t="inlineStr">
         <is>
           <t>Bureau de Greg</t>
         </is>
       </c>
-      <c r="C56" s="37" t="inlineStr">
+      <c r="C57" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D56" s="37" t="inlineStr">
+      <c r="D57" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E56" s="37" t="inlineStr">
+      <c r="E57" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS A. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F56" s="37" t="inlineStr">
+      <c r="F57" s="37" t="inlineStr">
         <is>
           <t>Vous avez désormais intérrogé tous les témoins officiels. Analysez les 4 lettres que vous avez trouvé pour continuer votre enquête.</t>
         </is>
       </c>
-      <c r="G56" s="37" t="n"/>
-    </row>
-    <row r="57" ht="30" customFormat="1" customHeight="1" s="44">
-      <c r="A57" s="43" t="inlineStr">
+      <c r="G57" s="37" t="n"/>
+    </row>
+    <row r="58" ht="30" customFormat="1" customHeight="1" s="36">
+      <c r="A58" s="43" t="inlineStr">
         <is>
           <t>E13</t>
         </is>
       </c>
-      <c r="B57" s="43" t="inlineStr">
+      <c r="B58" s="43" t="inlineStr">
         <is>
           <t>Bureau de Greg</t>
         </is>
       </c>
-      <c r="C57" s="43" t="inlineStr">
+      <c r="C58" s="43" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D57" s="43" t="inlineStr">
+      <c r="D58" s="43" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E57" s="43" t="inlineStr">
+      <c r="E58" s="43" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B.</t>
         </is>
       </c>
-      <c r="F57" s="43" t="inlineStr">
+      <c r="F58" s="43" t="inlineStr">
         <is>
           <t>Suivez le chemin indiqué pour aller interroger votre prochain témoin. Des indices se cachent sur la route.</t>
         </is>
       </c>
-      <c r="G57" s="43" t="n"/>
-    </row>
-    <row r="58" ht="30" customFormat="1" customHeight="1" s="36">
-      <c r="A58" s="34" t="inlineStr">
+      <c r="G58" s="43" t="n"/>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="34" t="inlineStr">
         <is>
           <t>E14</t>
         </is>
       </c>
-      <c r="B58" s="34" t="inlineStr">
+      <c r="B59" s="34" t="inlineStr">
         <is>
           <t>LE BOTANISTE</t>
         </is>
       </c>
-      <c r="C58" s="34" t="inlineStr">
+      <c r="C59" s="34" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D58" s="34" t="inlineStr">
+      <c r="D59" s="34" t="inlineStr">
         <is>
           <t>1. Vidéo du botaniste</t>
         </is>
       </c>
-      <c r="E58" s="35" t="inlineStr">
+      <c r="E59" s="35" t="inlineStr">
         <is>
           <t>La vidéo se lance tout de suite après le scan</t>
         </is>
       </c>
-      <c r="F58" s="34" t="n"/>
-      <c r="G58" s="34" t="n"/>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>E14</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t>LE BOTANISTE</t>
-        </is>
-      </c>
-      <c r="C59" s="11" t="inlineStr">
-        <is>
-          <t>les deux</t>
-        </is>
-      </c>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>2. Legende du media</t>
-        </is>
-      </c>
-      <c r="E59" s="11" t="inlineStr">
-        <is>
-          <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
-        </is>
-      </c>
-      <c r="F59" s="12" t="inlineStr">
-        <is>
-          <t>"…", botaniste au Parc Zoologique et Botanique de Mulhouse</t>
-        </is>
-      </c>
-      <c r="G59" s="12" t="n"/>
+      <c r="F59" s="34" t="n"/>
+      <c r="G59" s="34" t="n"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
@@ -3621,133 +3621,133 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
+          <t>LE BOTANISTE</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>les deux</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>2. Legende du media</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>"…", botaniste au Parc Zoologique et Botanique de Mulhouse</t>
+        </is>
+      </c>
+      <c r="G60" s="12" t="n"/>
+    </row>
+    <row r="61" ht="30" customFormat="1" customHeight="1" s="39">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
           <t>Le botaniste</t>
         </is>
       </c>
-      <c r="C60" s="11" t="inlineStr">
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="D61" s="11" t="inlineStr">
         <is>
           <t>3. Texte ou epreuve</t>
         </is>
       </c>
-      <c r="E60" s="11" t="inlineStr">
+      <c r="E61" s="11" t="inlineStr">
         <is>
           <t>Le coeur de l'etape : le temoignage ecrit, la consigne de l'epreuve, ou l'indice. Aussi long que necessaire.</t>
         </is>
       </c>
-      <c r="F60" s="12" t="inlineStr">
+      <c r="F61" s="12" t="inlineStr">
         <is>
           <t>Pour pénetrer dans la serre vous aurez besoin de transformer vos 4 lettres en chiffres</t>
         </is>
       </c>
-      <c r="G60" s="12" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>on créera cette épreuve sur une seule page plus tard, probablement avec un visuel.</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="30" customFormat="1" customHeight="1" s="39">
-      <c r="A61" s="37" t="inlineStr">
+    <row r="62" ht="30" customFormat="1" customHeight="1" s="44">
+      <c r="A62" s="37" t="inlineStr">
         <is>
           <t>E14</t>
         </is>
       </c>
-      <c r="B61" s="37" t="inlineStr">
+      <c r="B62" s="37" t="inlineStr">
         <is>
           <t>Le botaniste</t>
         </is>
       </c>
-      <c r="C61" s="37" t="inlineStr">
+      <c r="C62" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D61" s="37" t="inlineStr">
+      <c r="D62" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E61" s="37" t="inlineStr">
+      <c r="E62" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS A. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F61" s="37" t="inlineStr">
+      <c r="F62" s="37" t="inlineStr">
         <is>
           <t>Pénétrez dans la serre</t>
         </is>
       </c>
-      <c r="G61" s="37" t="n"/>
-    </row>
-    <row r="62" ht="30" customFormat="1" customHeight="1" s="44">
-      <c r="A62" s="43" t="inlineStr">
+      <c r="G62" s="37" t="n"/>
+    </row>
+    <row r="63" ht="48" customHeight="1">
+      <c r="A63" s="43" t="inlineStr">
         <is>
           <t>E14</t>
         </is>
       </c>
-      <c r="B62" s="43" t="inlineStr">
+      <c r="B63" s="43" t="inlineStr">
         <is>
           <t>Le botaniste</t>
         </is>
       </c>
-      <c r="C62" s="43" t="inlineStr">
+      <c r="C63" s="43" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D62" s="43" t="inlineStr">
+      <c r="D63" s="43" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E62" s="43" t="inlineStr">
+      <c r="E63" s="43" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B.</t>
         </is>
       </c>
-      <c r="F62" s="43" t="inlineStr">
+      <c r="F63" s="43" t="inlineStr">
         <is>
           <t>Pénétrez dans la serre</t>
         </is>
       </c>
-      <c r="G62" s="43" t="n"/>
-    </row>
-    <row r="63" ht="48" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>E15</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t>La serre</t>
-        </is>
-      </c>
-      <c r="C63" s="11" t="inlineStr">
-        <is>
-          <t>les deux</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>1. Accueil apres le scan</t>
-        </is>
-      </c>
-      <c r="E63" s="11" t="inlineStr">
-        <is>
-          <t>La phrase d'accroche affichee juste apres le scan, au-dessus du bouton. Une ou deux lignes, pas plus : le groupe est debout, il n'a pas envie de lire.</t>
-        </is>
-      </c>
-      <c r="F63" s="12" t="inlineStr">
-        <is>
-          <t>Félicitations, vous êtes à deux doigts d'élucider le mystère de la disparition d'Isabelle. Une scène se joue sous vos yeux, prenez le temps d'observer ce qu'il s'y passe et appuyez sur suivant</t>
-        </is>
-      </c>
-      <c r="G63" s="12" t="n"/>
+      <c r="G63" s="43" t="n"/>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
@@ -3767,185 +3767,218 @@
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
+          <t>1. Accueil apres le scan</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>La phrase d'accroche affichee juste apres le scan, au-dessus du bouton. Une ou deux lignes, pas plus : le groupe est debout, il n'a pas envie de lire.</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>Félicitations, vous êtes à deux doigts d'élucider le mystère de la disparition d'Isabelle. Une scène se joue sous vos yeux, prenez le temps d'observer ce qu'il s'y passe et appuyez sur suivant</t>
+        </is>
+      </c>
+      <c r="G64" s="12" t="n"/>
+    </row>
+    <row r="65" ht="30" customFormat="1" customHeight="1" s="36">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>La serre</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>les deux</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
           <t>3. Texte ou epreuve</t>
         </is>
       </c>
-      <c r="E64" s="11" t="inlineStr">
+      <c r="E65" s="11" t="inlineStr">
         <is>
           <t>Le coeur de l'etape : le temoignage ecrit, la consigne de l'epreuve, ou l'indice. Aussi long que necessaire.</t>
         </is>
       </c>
-      <c r="F64" s="12" t="inlineStr">
+      <c r="F65" s="12" t="inlineStr">
         <is>
           <t>Veuillez nous donner les conclusions de votr enquête. Qu'est arrivé à Isabelle ?</t>
         </is>
       </c>
-      <c r="G64" s="12" t="inlineStr">
+      <c r="G65" s="12" t="inlineStr">
         <is>
           <t>Champ IA pour donner ses conclusions</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="30" customFormat="1" customHeight="1" s="36">
-      <c r="A65" s="34" t="inlineStr">
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="34" t="inlineStr">
         <is>
           <t>E15</t>
         </is>
       </c>
-      <c r="B65" s="34" t="inlineStr">
+      <c r="B66" s="34" t="inlineStr">
         <is>
           <t>La serre</t>
         </is>
       </c>
-      <c r="C65" s="34" t="inlineStr">
+      <c r="C66" s="34" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D65" s="34" t="inlineStr">
+      <c r="D66" s="34" t="inlineStr">
         <is>
           <t>4. Vidéo point of view</t>
         </is>
       </c>
-      <c r="E65" s="34" t="inlineStr">
+      <c r="E66" s="34" t="inlineStr">
         <is>
           <t>La vidéo se lance tout de suite après le bouton suivant</t>
         </is>
       </c>
-      <c r="F65" s="34" t="n"/>
-      <c r="G65" s="34" t="inlineStr">
+      <c r="F66" s="34" t="n"/>
+      <c r="G66" s="34" t="inlineStr">
         <is>
           <t>point of view de la soirée d'Isabelle</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
+    <row r="67" ht="30" customFormat="1" customHeight="1" s="36">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>E15</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>La serre</t>
         </is>
       </c>
-      <c r="C66" s="11" t="inlineStr">
+      <c r="C67" s="11" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D66" s="11" t="inlineStr">
+      <c r="D67" s="11" t="inlineStr">
         <is>
           <t>5. Finish</t>
         </is>
       </c>
-      <c r="E66" s="11" t="inlineStr">
+      <c r="E67" s="11" t="inlineStr">
         <is>
           <t>Message final à délivrer en fonction des conclusions du groupe dans le champs IA</t>
         </is>
       </c>
-      <c r="F66" s="12" t="n"/>
-      <c r="G66" s="12" t="inlineStr">
+      <c r="F67" s="12" t="n"/>
+      <c r="G67" s="12" t="inlineStr">
         <is>
           <t>3 messages de félicitations (parfait - presque - dommage)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="30" customFormat="1" customHeight="1" s="36">
-      <c r="A67" s="34" t="inlineStr">
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="34" t="inlineStr">
         <is>
           <t>E16</t>
         </is>
       </c>
-      <c r="B67" s="34" t="inlineStr">
+      <c r="B68" s="34" t="inlineStr">
         <is>
           <t>Greg, version sens B</t>
         </is>
       </c>
-      <c r="C67" s="34" t="inlineStr">
+      <c r="C68" s="34" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D67" s="35" t="inlineStr">
+      <c r="D68" s="35" t="inlineStr">
         <is>
           <t>1. Vidéo de Greg</t>
         </is>
       </c>
-      <c r="E67" s="35" t="inlineStr">
+      <c r="E68" s="35" t="inlineStr">
         <is>
           <t>La vidéo se lance tout de suite après le scan</t>
         </is>
       </c>
-      <c r="F67" s="34" t="n"/>
-      <c r="G67" s="34" t="n"/>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
+      <c r="F68" s="34" t="n"/>
+      <c r="G68" s="34" t="n"/>
+    </row>
+    <row r="69" ht="30" customFormat="1" customHeight="1" s="39">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>E16</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>Greg, version sens B</t>
         </is>
       </c>
-      <c r="C68" s="11" t="inlineStr">
+      <c r="C69" s="11" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D68" s="11" t="inlineStr">
+      <c r="D69" s="11" t="inlineStr">
         <is>
           <t>2. Legende du media</t>
         </is>
       </c>
-      <c r="E68" s="11" t="inlineStr">
+      <c r="E69" s="11" t="inlineStr">
         <is>
           <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
         </is>
       </c>
-      <c r="F68" s="25" t="inlineStr">
+      <c r="F69" s="25" t="inlineStr">
         <is>
           <t>Greg, pas très rassurant</t>
         </is>
       </c>
-      <c r="G68" s="12" t="n"/>
-    </row>
-    <row r="69" ht="30" customFormat="1" customHeight="1" s="39">
-      <c r="A69" s="37" t="inlineStr">
+      <c r="G69" s="12" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="37" t="inlineStr">
         <is>
           <t>E16</t>
         </is>
       </c>
-      <c r="B69" s="37" t="inlineStr">
+      <c r="B70" s="37" t="inlineStr">
         <is>
           <t>Greg, version sens B</t>
         </is>
       </c>
-      <c r="C69" s="37" t="inlineStr">
+      <c r="C70" s="37" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D69" s="37" t="inlineStr">
+      <c r="D70" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E69" s="37" t="inlineStr">
+      <c r="E70" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F69" s="38" t="inlineStr">
+      <c r="F70" s="38" t="inlineStr">
         <is>
           <t>Rendez-vous dans la grande volière pour interroger Bill.</t>
         </is>
       </c>
-      <c r="G69" s="37" t="n"/>
+      <c r="G70" s="37" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Parcours" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Textes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Quiz" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pop quiz" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -693,13 +694,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="105" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="21" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -714,6 +716,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -735,10 +738,11 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>LES QUATRE ONGLETS, EN BAS DE L'ECRAN</t>
+          <t>LES CINQ ONGLETS, EN BAS DE L'ECRAN</t>
         </is>
       </c>
     </row>
@@ -770,88 +774,98 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="3" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="49" t="inlineStr">
+        <is>
+          <t>Pop quiz      ....  les questions bonus qui surgissent sans QR code pendant le parcours</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>CE QUE TU DOIS REMPLIR</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">     Les cases sur fond creme sont a remplir par toi.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="6" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">     Les cases sur fond gris sont calculees ou fixees, tu peux les ignorer.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="7" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">     Les cases sur fond rose sont des questions qui attendent ta reponse.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>AVANCEMENT</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21" ht="45" customHeight="1">
       <c r="B21" s="3" t="inlineStr">
         <is>
+          <t>AVANCEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
           <t>86 textes a ecrire au total, repartis sur les 17 etapes.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="8" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Astuce pour suivre ton avancement : clique sur la lettre F en haut de la colonne des textes, dans l'onglet Textes. En bas a droite de l'ecran, Excel affiche le nombre de cases remplies.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="75" customHeight="1">
-      <c r="B24" s="3" t="inlineStr">
+    <row r="24" ht="75" customHeight="1"/>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>QUATRE QUESTIONS AVANT QUE JE FABRIQUE QUOI QUE CE SOIT</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="13" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">1. COMBIEN DE QR CODES ? </t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1"/>
-    <row r="27">
-      <c r="B27" s="9" t="inlineStr">
+    <row r="27"/>
+    <row r="28" ht="45" customHeight="1">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>2. LES LETTRES DE L'ENIGME. En sens B, le joueur ramasse I, R, I, S dans cet ordre : le mot est deja ecrit, l'enigme du Jardin des Iris se resout sans reflechir. En sens A il ramasse R, I, S, I et doit chercher. Veux-tu permuter deux lettres pour reequilibrer ?</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="45" customHeight="1"/>
-    <row r="29">
-      <c r="B29" s="9" t="inlineStr">
+    <row r="29"/>
+    <row r="30" ht="75" customHeight="1">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>3. LE CODE DE LA SERRE. Le joueur tape-t-il IRIS sur le site, ou sur un cadenas physique ? Si c'est sur le site, c'est une mecanique a construire, dis-le moi.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="75" customHeight="1"/>
-    <row r="31">
-      <c r="B31" s="9" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>4. LES DEUX PISTES DE LA COLLEGUE SOIGNEUSE. Sur ton schema, elle ouvre deux branches : les cameras puis le plan d'un cote, les jumelles puis l'enclos des loups de l'autre. Les deux sont-elles obligatoires, ou la premiere est-elle facultative ? J'ai suppose qu'on les fait l'une apres l'autre.</t>
         </is>
@@ -4379,4 +4393,292 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="56" customHeight="1">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>LES QUESTIONS BONUS. Elles surgissent sans QR code, pendant le parcours. Une seule tentative : qui répond juste du premier coup gagne un indice que les autres n'auront pas. « Moment » vaut « au scan » (dès l'ouverture de la borne) ou « avant la sortie » (juste avant l'écran qui indique où aller). Une proposition laissée vide est ignorée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="51" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B2" s="51" t="inlineStr">
+        <is>
+          <t>Moment</t>
+        </is>
+      </c>
+      <c r="C2" s="51" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="D2" s="51" t="inlineStr">
+        <is>
+          <t>Proposition 1</t>
+        </is>
+      </c>
+      <c r="E2" s="51" t="inlineStr">
+        <is>
+          <t>Proposition 2</t>
+        </is>
+      </c>
+      <c r="F2" s="51" t="inlineStr">
+        <is>
+          <t>Proposition 3</t>
+        </is>
+      </c>
+      <c r="G2" s="51" t="inlineStr">
+        <is>
+          <t>Proposition 4</t>
+        </is>
+      </c>
+      <c r="H2" s="51" t="inlineStr">
+        <is>
+          <t>Bonne reponse (le numero)</t>
+        </is>
+      </c>
+      <c r="I2" s="51" t="inlineStr">
+        <is>
+          <t>Indice gagne</t>
+        </is>
+      </c>
+      <c r="J2" s="51" t="inlineStr">
+        <is>
+          <t>Message si faux</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="46" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>au scan</t>
+        </is>
+      </c>
+      <c r="C3" s="52" t="inlineStr">
+        <is>
+          <t>Sous son épais pelage blanc, de quelle couleur est la peau de l'ours polaire ?</t>
+        </is>
+      </c>
+      <c r="D3" s="52" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="E3" s="52" t="inlineStr">
+        <is>
+          <t>Blanche</t>
+        </is>
+      </c>
+      <c r="F3" s="52" t="inlineStr">
+        <is>
+          <t>Noire</t>
+        </is>
+      </c>
+      <c r="G3" s="52" t="inlineStr">
+        <is>
+          <t>Grise</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="52" t="inlineStr">
+        <is>
+          <t>Félicitations ! Voici votre indice : le Talkie Walkie des soigneurs est branché sur un circuit fermé, seuls les membres de l'équipe du zoo peuvent l'utiliser.</t>
+        </is>
+      </c>
+      <c r="J3" s="52" t="inlineStr">
+        <is>
+          <t>Mauvaise réponse. Ne vous inquiétez pas, d'autres questions surprises vous seront proposées plus tard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="46" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>au scan</t>
+        </is>
+      </c>
+      <c r="C4" s="52" t="inlineStr">
+        <is>
+          <t>Dans une meute de loups du Canada, qui décide du moment de la chasse ?</t>
+        </is>
+      </c>
+      <c r="D4" s="52" t="inlineStr">
+        <is>
+          <t>Le loup le plus fort</t>
+        </is>
+      </c>
+      <c r="E4" s="52" t="inlineStr">
+        <is>
+          <t>Le couple de parents</t>
+        </is>
+      </c>
+      <c r="F4" s="52" t="inlineStr">
+        <is>
+          <t>Le plus vieux loup</t>
+        </is>
+      </c>
+      <c r="G4" s="52" t="inlineStr">
+        <is>
+          <t>Chacun à tour de rôle</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" s="52" t="inlineStr">
+        <is>
+          <t>Félicitations ! Voici votre indice : Un intrus s'est introduit dans le Parc Zoologique &amp; Botanique cette nuit et peut semer la zizanie dans votre enquête.</t>
+        </is>
+      </c>
+      <c r="J4" s="52" t="inlineStr">
+        <is>
+          <t>Mauvaise réponse. Ne vous inquiétez pas, d'autres questions surprises vous seront proposées plus tard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>E09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avant la sortie</t>
+        </is>
+      </c>
+      <c r="C5" s="52" t="inlineStr">
+        <is>
+          <t>Pourquoi des industriels mulhousiens ont-ils créé ce parc en 1868 ?</t>
+        </is>
+      </c>
+      <c r="D5" s="52" t="inlineStr">
+        <is>
+          <t>Pour offrir un lieu de détente à leurs ouvriers</t>
+        </is>
+      </c>
+      <c r="E5" s="52" t="inlineStr">
+        <is>
+          <t>Pour recueillir les animaux d'un cirque en faillite</t>
+        </is>
+      </c>
+      <c r="F5" s="52" t="inlineStr">
+        <is>
+          <t>Pour y élever des animaux de ferme</t>
+        </is>
+      </c>
+      <c r="G5" s="52" t="inlineStr">
+        <is>
+          <t>Pour en faire une réserve de chasse</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="52" t="inlineStr">
+        <is>
+          <t>Félicitations ! Voici votre indice : Cet interrogatoire était un peu suspect, n'est-ce pas ? Je me demande si Greg est digne de confiance.</t>
+        </is>
+      </c>
+      <c r="J5" s="52" t="inlineStr">
+        <is>
+          <t>Mauvaise réponse. Ne vous inquiétez pas, d'autres questions surprises vous seront proposées plus tard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avant la sortie</t>
+        </is>
+      </c>
+      <c r="C6" s="52" t="inlineStr">
+        <is>
+          <t>Pourquoi des industriels mulhousiens ont-ils créé ce parc en 1868 ?</t>
+        </is>
+      </c>
+      <c r="D6" s="52" t="inlineStr">
+        <is>
+          <t>Pour offrir un lieu de détente à leurs ouvriers</t>
+        </is>
+      </c>
+      <c r="E6" s="52" t="inlineStr">
+        <is>
+          <t>Pour recueillir les animaux d'un cirque en faillite</t>
+        </is>
+      </c>
+      <c r="F6" s="52" t="inlineStr">
+        <is>
+          <t>Pour y élever des animaux de ferme</t>
+        </is>
+      </c>
+      <c r="G6" s="52" t="inlineStr">
+        <is>
+          <t>Pour en faire une réserve de chasse</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="52" t="inlineStr">
+        <is>
+          <t>Félicitations ! Voici votre indice : Cet interrogatoire était un peu suspect, n'est-ce pas ? Je me demande si Greg est digne de confiance.</t>
+        </is>
+      </c>
+      <c r="J6" s="52" t="inlineStr">
+        <is>
+          <t>Mauvaise réponse. Ne vous inquiétez pas, d'autres questions surprises vous seront proposées plus tard.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -694,14 +694,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="B2:B32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="105" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="21" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -716,7 +715,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -738,7 +736,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -781,7 +778,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -810,7 +806,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="45" customHeight="1">
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -847,7 +842,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="45" customHeight="1">
       <c r="B28" s="9" t="inlineStr">
         <is>
@@ -855,7 +849,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30" ht="75" customHeight="1">
       <c r="B30" s="9" t="inlineStr">
         <is>
@@ -863,7 +856,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="B32" s="9" t="inlineStr">
         <is>
@@ -1703,7 +1695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2892,7 +2884,7 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>Vous l'aurez compris, un animal a semé la zizanie dans le parc hier soir. Saurez-vous l'identifier sur ce panneau ?</t>
+          <t>/</t>
         </is>
       </c>
       <c r="G37" s="12" t="n"/>
@@ -2925,7 +2917,7 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>Quel est le numéro de l'animal qui était présent dans le zoo hier soir ?</t>
+          <t>Enquêteur ! Vous venez de tomber sur une empreinte suspecte. Saurez-vous reconnaître à qui elle appartient ? Notez le numéro correspondant ci-dessous.</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
@@ -3251,113 +3243,109 @@
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>Qu'est-ce que c'est que ce sac ? Observez bien son contenu.</t>
+          <t>Vous venez de tomber sur un sac qui ne semble pas être à sa place. Cliquez sur « Voir » pour faire défiler son contenu.</t>
         </is>
       </c>
       <c r="G48" s="12" t="n"/>
     </row>
     <row r="49" ht="30" customFormat="1" customHeight="1" s="44">
-      <c r="A49" s="38" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>E11</t>
         </is>
       </c>
-      <c r="B49" s="37" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Indice : Le sac du botaniste</t>
         </is>
       </c>
-      <c r="C49" s="37" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>les deux</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3. Texte ou epreuve</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Le coeur de l'etape.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Certains objets portaient un chiffre. Dans l'ordre où vous les avez vus, ils forment un nombre à quatre chiffres.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="38" t="inlineStr">
+        <is>
+          <t>E11</t>
+        </is>
+      </c>
+      <c r="B50" s="37" t="inlineStr">
+        <is>
+          <t>Indice : Le sac du botaniste</t>
+        </is>
+      </c>
+      <c r="C50" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D49" s="37" t="inlineStr">
+      <c r="D50" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E49" s="37" t="inlineStr">
+      <c r="E50" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS A. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F49" s="37" t="inlineStr">
+      <c r="F50" s="37" t="inlineStr">
         <is>
           <t>Suivez le chemin indiqué pour poursuivre l'enquête</t>
         </is>
       </c>
-      <c r="G49" s="37" t="n"/>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="45" t="inlineStr">
+      <c r="G50" s="37" t="n"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="45" t="inlineStr">
         <is>
           <t>E11</t>
         </is>
       </c>
-      <c r="B50" s="43" t="inlineStr">
+      <c r="B51" s="43" t="inlineStr">
         <is>
           <t>Indice : Le sac du botaniste</t>
         </is>
       </c>
-      <c r="C50" s="43" t="inlineStr">
+      <c r="C51" s="43" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D50" s="43" t="inlineStr">
+      <c r="D51" s="43" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E50" s="43" t="inlineStr">
+      <c r="E51" s="43" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B.</t>
         </is>
       </c>
-      <c r="F50" s="43" t="inlineStr">
+      <c r="F51" s="43" t="inlineStr">
         <is>
           <t>Suivez le chemin indiqué pour poursuivre l'enquête</t>
         </is>
       </c>
-      <c r="G50" s="43" t="n"/>
-    </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t>Appel du commissaire</t>
-        </is>
-      </c>
-      <c r="C51" s="11" t="inlineStr">
-        <is>
-          <t>les deux</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>1. Accueil apres le scan</t>
-        </is>
-      </c>
-      <c r="E51" s="11" t="inlineStr">
-        <is>
-          <t>La phrase d'accroche affichee juste apres le scan, au-dessus du bouton. Une ou deux lignes, pas plus : le groupe est debout, il n'a pas envie de lire.</t>
-        </is>
-      </c>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>Vous avez un appel entrant du Commissaire Jean</t>
-        </is>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>sonnerie émise, il faudrait que les gens puisse toucher le bouton "décrocher pour déclencher l'audio"</t>
-        </is>
-      </c>
+      <c r="G51" s="43" t="n"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
@@ -3377,20 +3365,24 @@
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>2. Legende du media</t>
+          <t>1. Accueil apres le scan</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
+          <t>La phrase d'accroche affichee juste apres le scan, au-dessus du bouton. Une ou deux lignes, pas plus : le groupe est debout, il n'a pas envie de lire.</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>Commissaire Jean, dubitatif</t>
-        </is>
-      </c>
-      <c r="G52" s="12" t="n"/>
+          <t>Vous avez un appel entrant du Commissaire Jean</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>sonnerie émise, il faudrait que les gens puisse toucher le bouton "décrocher pour déclencher l'audio"</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="30" customFormat="1" customHeight="1" s="39">
       <c r="A53" s="11" t="inlineStr">
@@ -3410,255 +3402,255 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
+          <t>2. Legende du media</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>Commissaire Jean, dubitatif</t>
+        </is>
+      </c>
+      <c r="G53" s="12" t="n"/>
+    </row>
+    <row r="54" ht="30" customFormat="1" customHeight="1" s="44">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>E12</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Appel du commissaire</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>les deux</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
           <t>3. Texte ou epreuve</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E54" s="11" t="inlineStr">
         <is>
           <t>Le coeur de l'etape : le temoignage ecrit, la consigne de l'epreuve, ou l'indice. Aussi long que necessaire.</t>
         </is>
       </c>
-      <c r="F53" s="12" t="inlineStr">
+      <c r="F54" s="12" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="G53" s="12" t="inlineStr">
+      <c r="G54" s="12" t="inlineStr">
         <is>
           <t>Fichier audio</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customFormat="1" customHeight="1" s="44">
-      <c r="A54" s="37" t="inlineStr">
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="37" t="inlineStr">
         <is>
           <t>E12</t>
         </is>
       </c>
-      <c r="B54" s="37" t="inlineStr">
+      <c r="B55" s="37" t="inlineStr">
         <is>
           <t>Appel du commissaire</t>
         </is>
       </c>
-      <c r="C54" s="37" t="inlineStr">
+      <c r="C55" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D54" s="37" t="inlineStr">
+      <c r="D55" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E54" s="37" t="inlineStr">
+      <c r="E55" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS A. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F54" s="37" t="inlineStr">
+      <c r="F55" s="37" t="inlineStr">
         <is>
           <t>Poursuivez jusqu'au bureau de Greg</t>
         </is>
       </c>
-      <c r="G54" s="37" t="n"/>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="43" t="inlineStr">
+      <c r="G55" s="37" t="n"/>
+    </row>
+    <row r="56" ht="30" customFormat="1" customHeight="1" s="39">
+      <c r="A56" s="43" t="inlineStr">
         <is>
           <t>E12</t>
         </is>
       </c>
-      <c r="B55" s="43" t="inlineStr">
+      <c r="B56" s="43" t="inlineStr">
         <is>
           <t>Appel du commissaire</t>
         </is>
       </c>
-      <c r="C55" s="43" t="inlineStr">
+      <c r="C56" s="43" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D55" s="43" t="inlineStr">
+      <c r="D56" s="43" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E55" s="43" t="inlineStr">
+      <c r="E56" s="43" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B.</t>
         </is>
       </c>
-      <c r="F55" s="43" t="inlineStr">
+      <c r="F56" s="43" t="inlineStr">
         <is>
           <t>Poursuivez jusqu'au bureau de Greg</t>
         </is>
       </c>
-      <c r="G55" s="43" t="n"/>
-    </row>
-    <row r="56" ht="30" customFormat="1" customHeight="1" s="39">
-      <c r="A56" s="11" t="inlineStr">
+      <c r="G56" s="43" t="n"/>
+    </row>
+    <row r="57" ht="30" customFormat="1" customHeight="1" s="44">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>E13</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>Bureau de Greg</t>
         </is>
       </c>
-      <c r="C56" s="11" t="inlineStr">
+      <c r="C57" s="11" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="D57" s="11" t="inlineStr">
         <is>
           <t>1. Accueil apres le scan</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr">
+      <c r="E57" s="11" t="inlineStr">
         <is>
           <t>La phrase d'accroche affichee juste apres le scan, au-dessus du bouton. Une ou deux lignes, pas plus : le groupe est debout, il n'a pas envie de lire.</t>
         </is>
       </c>
-      <c r="F56" s="12" t="inlineStr">
+      <c r="F57" s="12" t="inlineStr">
         <is>
           <t>Observez le bureau de Greg à la recherche d'indices</t>
         </is>
       </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t>ils trouvent un indice supplémentaire</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="30" customFormat="1" customHeight="1" s="44">
-      <c r="A57" s="37" t="inlineStr">
+    <row r="58" ht="30" customFormat="1" customHeight="1" s="36">
+      <c r="A58" s="37" t="inlineStr">
         <is>
           <t>E13</t>
         </is>
       </c>
-      <c r="B57" s="37" t="inlineStr">
+      <c r="B58" s="37" t="inlineStr">
         <is>
           <t>Bureau de Greg</t>
         </is>
       </c>
-      <c r="C57" s="37" t="inlineStr">
+      <c r="C58" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D57" s="37" t="inlineStr">
+      <c r="D58" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E57" s="37" t="inlineStr">
+      <c r="E58" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS A. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F57" s="37" t="inlineStr">
+      <c r="F58" s="37" t="inlineStr">
         <is>
           <t>Vous avez désormais intérrogé tous les témoins officiels. Analysez les 4 lettres que vous avez trouvé pour continuer votre enquête.</t>
         </is>
       </c>
-      <c r="G57" s="37" t="n"/>
-    </row>
-    <row r="58" ht="30" customFormat="1" customHeight="1" s="36">
-      <c r="A58" s="43" t="inlineStr">
+      <c r="G58" s="37" t="n"/>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="43" t="inlineStr">
         <is>
           <t>E13</t>
         </is>
       </c>
-      <c r="B58" s="43" t="inlineStr">
+      <c r="B59" s="43" t="inlineStr">
         <is>
           <t>Bureau de Greg</t>
         </is>
       </c>
-      <c r="C58" s="43" t="inlineStr">
+      <c r="C59" s="43" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D58" s="43" t="inlineStr">
+      <c r="D59" s="43" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E58" s="43" t="inlineStr">
+      <c r="E59" s="43" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B.</t>
         </is>
       </c>
-      <c r="F58" s="43" t="inlineStr">
+      <c r="F59" s="43" t="inlineStr">
         <is>
           <t>Suivez le chemin indiqué pour aller interroger votre prochain témoin. Des indices se cachent sur la route.</t>
         </is>
       </c>
-      <c r="G58" s="43" t="n"/>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="34" t="inlineStr">
+      <c r="G59" s="43" t="n"/>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="34" t="inlineStr">
         <is>
           <t>E14</t>
         </is>
       </c>
-      <c r="B59" s="34" t="inlineStr">
+      <c r="B60" s="34" t="inlineStr">
         <is>
           <t>LE BOTANISTE</t>
         </is>
       </c>
-      <c r="C59" s="34" t="inlineStr">
+      <c r="C60" s="34" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D59" s="34" t="inlineStr">
+      <c r="D60" s="34" t="inlineStr">
         <is>
           <t>1. Vidéo du botaniste</t>
         </is>
       </c>
-      <c r="E59" s="35" t="inlineStr">
+      <c r="E60" s="35" t="inlineStr">
         <is>
           <t>La vidéo se lance tout de suite après le scan</t>
         </is>
       </c>
-      <c r="F59" s="34" t="n"/>
-      <c r="G59" s="34" t="n"/>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t>E14</t>
-        </is>
-      </c>
-      <c r="B60" s="11" t="inlineStr">
-        <is>
-          <t>LE BOTANISTE</t>
-        </is>
-      </c>
-      <c r="C60" s="11" t="inlineStr">
-        <is>
-          <t>les deux</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>2. Legende du media</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
-        </is>
-      </c>
-      <c r="F60" s="12" t="inlineStr">
-        <is>
-          <t>"…", botaniste au Parc Zoologique et Botanique de Mulhouse</t>
-        </is>
-      </c>
-      <c r="G60" s="12" t="n"/>
+      <c r="F60" s="34" t="n"/>
+      <c r="G60" s="34" t="n"/>
     </row>
     <row r="61" ht="30" customFormat="1" customHeight="1" s="39">
       <c r="A61" s="11" t="inlineStr">
@@ -3668,133 +3660,133 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
+          <t>LE BOTANISTE</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>les deux</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>2. Legende du media</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>"…", botaniste au Parc Zoologique et Botanique de Mulhouse</t>
+        </is>
+      </c>
+      <c r="G61" s="12" t="n"/>
+    </row>
+    <row r="62" ht="30" customFormat="1" customHeight="1" s="44">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
           <t>Le botaniste</t>
         </is>
       </c>
-      <c r="C61" s="11" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D61" s="11" t="inlineStr">
+      <c r="D62" s="11" t="inlineStr">
         <is>
           <t>3. Texte ou epreuve</t>
         </is>
       </c>
-      <c r="E61" s="11" t="inlineStr">
+      <c r="E62" s="11" t="inlineStr">
         <is>
           <t>Le coeur de l'etape : le temoignage ecrit, la consigne de l'epreuve, ou l'indice. Aussi long que necessaire.</t>
         </is>
       </c>
-      <c r="F61" s="12" t="inlineStr">
-        <is>
-          <t>Pour pénetrer dans la serre vous aurez besoin de transformer vos 4 lettres en chiffres</t>
-        </is>
-      </c>
-      <c r="G61" s="12" t="inlineStr">
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>Pour pénétrer dans la serre, entrez le code que vous avez trouvé un peu plus tôt.</t>
+        </is>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
         <is>
           <t>on créera cette épreuve sur une seule page plus tard, probablement avec un visuel.</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="30" customFormat="1" customHeight="1" s="44">
-      <c r="A62" s="37" t="inlineStr">
+    <row r="63" ht="48" customHeight="1">
+      <c r="A63" s="37" t="inlineStr">
         <is>
           <t>E14</t>
         </is>
       </c>
-      <c r="B62" s="37" t="inlineStr">
+      <c r="B63" s="37" t="inlineStr">
         <is>
           <t>Le botaniste</t>
         </is>
       </c>
-      <c r="C62" s="37" t="inlineStr">
+      <c r="C63" s="37" t="inlineStr">
         <is>
           <t>sens A</t>
         </is>
       </c>
-      <c r="D62" s="37" t="inlineStr">
+      <c r="D63" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E62" s="37" t="inlineStr">
+      <c r="E63" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS A. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F62" s="37" t="inlineStr">
+      <c r="F63" s="37" t="inlineStr">
         <is>
           <t>Pénétrez dans la serre</t>
         </is>
       </c>
-      <c r="G62" s="37" t="n"/>
-    </row>
-    <row r="63" ht="48" customHeight="1">
-      <c r="A63" s="43" t="inlineStr">
+      <c r="G63" s="37" t="n"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="43" t="inlineStr">
         <is>
           <t>E14</t>
         </is>
       </c>
-      <c r="B63" s="43" t="inlineStr">
+      <c r="B64" s="43" t="inlineStr">
         <is>
           <t>Le botaniste</t>
         </is>
       </c>
-      <c r="C63" s="43" t="inlineStr">
+      <c r="C64" s="43" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D63" s="43" t="inlineStr">
+      <c r="D64" s="43" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E63" s="43" t="inlineStr">
+      <c r="E64" s="43" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B.</t>
         </is>
       </c>
-      <c r="F63" s="43" t="inlineStr">
+      <c r="F64" s="43" t="inlineStr">
         <is>
           <t>Pénétrez dans la serre</t>
         </is>
       </c>
-      <c r="G63" s="43" t="n"/>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t>E15</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="inlineStr">
-        <is>
-          <t>La serre</t>
-        </is>
-      </c>
-      <c r="C64" s="11" t="inlineStr">
-        <is>
-          <t>les deux</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>1. Accueil apres le scan</t>
-        </is>
-      </c>
-      <c r="E64" s="11" t="inlineStr">
-        <is>
-          <t>La phrase d'accroche affichee juste apres le scan, au-dessus du bouton. Une ou deux lignes, pas plus : le groupe est debout, il n'a pas envie de lire.</t>
-        </is>
-      </c>
-      <c r="F64" s="12" t="inlineStr">
-        <is>
-          <t>Félicitations, vous êtes à deux doigts d'élucider le mystère de la disparition d'Isabelle. Une scène se joue sous vos yeux, prenez le temps d'observer ce qu'il s'y passe et appuyez sur suivant</t>
-        </is>
-      </c>
-      <c r="G64" s="12" t="n"/>
+      <c r="G64" s="43" t="n"/>
     </row>
     <row r="65" ht="30" customFormat="1" customHeight="1" s="36">
       <c r="A65" s="11" t="inlineStr">
@@ -3814,185 +3806,218 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
+          <t>1. Accueil apres le scan</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>La phrase d'accroche affichee juste apres le scan, au-dessus du bouton. Une ou deux lignes, pas plus : le groupe est debout, il n'a pas envie de lire.</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>Félicitations, vous êtes à deux doigts d'élucider le mystère de la disparition d'Isabelle. Une scène se joue sous vos yeux, prenez le temps d'observer ce qu'il s'y passe et appuyez sur suivant</t>
+        </is>
+      </c>
+      <c r="G65" s="12" t="n"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>La serre</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>les deux</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
           <t>3. Texte ou epreuve</t>
         </is>
       </c>
-      <c r="E65" s="11" t="inlineStr">
+      <c r="E66" s="11" t="inlineStr">
         <is>
           <t>Le coeur de l'etape : le temoignage ecrit, la consigne de l'epreuve, ou l'indice. Aussi long que necessaire.</t>
         </is>
       </c>
-      <c r="F65" s="12" t="inlineStr">
+      <c r="F66" s="12" t="inlineStr">
         <is>
           <t>Veuillez nous donner les conclusions de votr enquête. Qu'est arrivé à Isabelle ?</t>
         </is>
       </c>
-      <c r="G65" s="12" t="inlineStr">
+      <c r="G66" s="12" t="inlineStr">
         <is>
           <t>Champ IA pour donner ses conclusions</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="34" t="inlineStr">
+    <row r="67" ht="30" customFormat="1" customHeight="1" s="36">
+      <c r="A67" s="34" t="inlineStr">
         <is>
           <t>E15</t>
         </is>
       </c>
-      <c r="B66" s="34" t="inlineStr">
+      <c r="B67" s="34" t="inlineStr">
         <is>
           <t>La serre</t>
         </is>
       </c>
-      <c r="C66" s="34" t="inlineStr">
+      <c r="C67" s="34" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D66" s="34" t="inlineStr">
+      <c r="D67" s="34" t="inlineStr">
         <is>
           <t>4. Vidéo point of view</t>
         </is>
       </c>
-      <c r="E66" s="34" t="inlineStr">
+      <c r="E67" s="34" t="inlineStr">
         <is>
           <t>La vidéo se lance tout de suite après le bouton suivant</t>
         </is>
       </c>
-      <c r="F66" s="34" t="n"/>
-      <c r="G66" s="34" t="inlineStr">
+      <c r="F67" s="34" t="n"/>
+      <c r="G67" s="34" t="inlineStr">
         <is>
           <t>point of view de la soirée d'Isabelle</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="30" customFormat="1" customHeight="1" s="36">
-      <c r="A67" s="11" t="inlineStr">
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>E15</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>La serre</t>
         </is>
       </c>
-      <c r="C67" s="11" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
         <is>
           <t>les deux</t>
         </is>
       </c>
-      <c r="D67" s="11" t="inlineStr">
+      <c r="D68" s="11" t="inlineStr">
         <is>
           <t>5. Finish</t>
         </is>
       </c>
-      <c r="E67" s="11" t="inlineStr">
+      <c r="E68" s="11" t="inlineStr">
         <is>
           <t>Message final à délivrer en fonction des conclusions du groupe dans le champs IA</t>
         </is>
       </c>
-      <c r="F67" s="12" t="n"/>
-      <c r="G67" s="12" t="inlineStr">
+      <c r="F68" s="12" t="n"/>
+      <c r="G68" s="12" t="inlineStr">
         <is>
           <t>3 messages de félicitations (parfait - presque - dommage)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="34" t="inlineStr">
+    <row r="69" ht="30" customFormat="1" customHeight="1" s="39">
+      <c r="A69" s="34" t="inlineStr">
         <is>
           <t>E16</t>
         </is>
       </c>
-      <c r="B68" s="34" t="inlineStr">
+      <c r="B69" s="34" t="inlineStr">
         <is>
           <t>Greg, version sens B</t>
         </is>
       </c>
-      <c r="C68" s="34" t="inlineStr">
+      <c r="C69" s="34" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D68" s="35" t="inlineStr">
+      <c r="D69" s="35" t="inlineStr">
         <is>
           <t>1. Vidéo de Greg</t>
         </is>
       </c>
-      <c r="E68" s="35" t="inlineStr">
+      <c r="E69" s="35" t="inlineStr">
         <is>
           <t>La vidéo se lance tout de suite après le scan</t>
         </is>
       </c>
-      <c r="F68" s="34" t="n"/>
-      <c r="G68" s="34" t="n"/>
-    </row>
-    <row r="69" ht="30" customFormat="1" customHeight="1" s="39">
-      <c r="A69" s="11" t="inlineStr">
+      <c r="F69" s="34" t="n"/>
+      <c r="G69" s="34" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>E16</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>Greg, version sens B</t>
         </is>
       </c>
-      <c r="C69" s="11" t="inlineStr">
+      <c r="C70" s="11" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D69" s="11" t="inlineStr">
+      <c r="D70" s="11" t="inlineStr">
         <is>
           <t>2. Legende du media</t>
         </is>
       </c>
-      <c r="E69" s="11" t="inlineStr">
+      <c r="E70" s="11" t="inlineStr">
         <is>
           <t>La phrase sous la video ou l'audio. Elle dit qui parle et de quoi. Une ligne.</t>
         </is>
       </c>
-      <c r="F69" s="25" t="inlineStr">
+      <c r="F70" s="25" t="inlineStr">
         <is>
           <t>Greg, pas très rassurant</t>
         </is>
       </c>
-      <c r="G69" s="12" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="37" t="inlineStr">
+      <c r="G70" s="12" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="37" t="inlineStr">
         <is>
           <t>E16</t>
         </is>
       </c>
-      <c r="B70" s="37" t="inlineStr">
+      <c r="B71" s="37" t="inlineStr">
         <is>
           <t>Greg, version sens B</t>
         </is>
       </c>
-      <c r="C70" s="37" t="inlineStr">
+      <c r="C71" s="37" t="inlineStr">
         <is>
           <t>sens B</t>
         </is>
       </c>
-      <c r="D70" s="37" t="inlineStr">
+      <c r="D71" s="37" t="inlineStr">
         <is>
           <t>4. Ou aller ensuite</t>
         </is>
       </c>
-      <c r="E70" s="37" t="inlineStr">
+      <c r="E71" s="37" t="inlineStr">
         <is>
           <t>La phrase qui envoie le joueur a l'etape suivante DU SENS B. C'est elle qui fait vivre les deux sens.</t>
         </is>
       </c>
-      <c r="F70" s="38" t="inlineStr">
+      <c r="F71" s="38" t="inlineStr">
         <is>
           <t>Rendez-vous dans la grande volière pour interroger Bill.</t>
         </is>
       </c>
-      <c r="G70" s="37" t="n"/>
+      <c r="G71" s="37" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Textes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Quiz" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Pop quiz" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Denouements" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -3279,7 +3280,6 @@
           <t>Certains objets portaient un chiffre. Dans l'ordre où vous les avez vus, ils forment un nombre à quatre chiffres.</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="38" t="inlineStr">
@@ -4706,4 +4706,150 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="78" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="72" customHeight="1">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>LES TROIS FINS DE L'ENQUETE. Elles sont essayees DE HAUT EN BAS : la premiere dont les conditions sont remplies l'emporte, et la derniere ligne sert de fin par defaut. Dans « Mots attendus », le point-virgule separe des idees qui doivent TOUTES etre presentes, la barre verticale separe des facons de dire la meme chose dont UNE SEULE suffit. Les accents, les majuscules et les fins de mots sont ignores : ecrire « endorm » attrape endormie, endormi et s'endormait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="51" t="inlineStr">
+        <is>
+          <t>Rang</t>
+        </is>
+      </c>
+      <c r="B2" s="51" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C2" s="51" t="inlineStr">
+        <is>
+          <t>Mots attendus</t>
+        </is>
+      </c>
+      <c r="D2" s="51" t="inlineStr">
+        <is>
+          <t>Mots qui disqualifient</t>
+        </is>
+      </c>
+      <c r="E2" s="51" t="inlineStr">
+        <is>
+          <t>Titre affiche</t>
+        </is>
+      </c>
+      <c r="F2" s="51" t="inlineStr">
+        <is>
+          <t>Texte du denouement</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="86" customHeight="1">
+      <c r="A3" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="50" t="inlineStr">
+        <is>
+          <t>Bon</t>
+        </is>
+      </c>
+      <c r="C3" s="50" t="inlineStr">
+        <is>
+          <t>tisane|valeriane|infusion|plante;endorm|sommeil|assoupi|dort|dormi;serre</t>
+        </is>
+      </c>
+      <c r="D3" s="50" t="inlineStr">
+        <is>
+          <t>tuee|assassin|meurtre|cadavre|kidnapp|enlevee|enleve par</t>
+        </is>
+      </c>
+      <c r="E3" s="50" t="inlineStr">
+        <is>
+          <t>Vous avez élucidé le mystère</t>
+        </is>
+      </c>
+      <c r="F3" s="50" t="inlineStr">
+        <is>
+          <t>C'est exactement cela. Isabelle a bu la tisane à la valériane de son collègue botaniste. Prise d'une grande fatigue, elle est retournée à la serre pour lui dire que le dosage était bien trop fort — et s'y est endormie. Personne n'a disparu, personne n'a été enlevé : elle dormait, à deux pas de tout le monde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="86" customHeight="1">
+      <c r="A4" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="50" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="C4" s="50" t="inlineStr">
+        <is>
+          <t>empoisonn|poison|intoxi|drogu|tisane|valeriane</t>
+        </is>
+      </c>
+      <c r="D4" s="50" t="inlineStr">
+        <is>
+          <t>tuee|assassin|meurtre|cadavre|kidnapp|enlevee|enleve par</t>
+        </is>
+      </c>
+      <c r="E4" s="50" t="inlineStr">
+        <is>
+          <t>Vous brûlez</t>
+        </is>
+      </c>
+      <c r="F4" s="50" t="inlineStr">
+        <is>
+          <t>Vous tenez le bon fil : la tisane du botaniste est bien à l'origine de tout. Mais il n'a empoisonné personne. Le dosage de valériane était trop fort, Isabelle s'est sentie épuisée, elle est retournée à la serre pour le lui dire, et s'y est endormie. Une maladresse, pas un crime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="86" customHeight="1">
+      <c r="A5" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="50" t="inlineStr">
+        <is>
+          <t>Mauvais</t>
+        </is>
+      </c>
+      <c r="C5" s="50" t="inlineStr"/>
+      <c r="D5" s="50" t="inlineStr"/>
+      <c r="E5" s="50" t="inlineStr">
+        <is>
+          <t>L'enquête reste ouverte</t>
+        </is>
+      </c>
+      <c r="F5" s="50" t="inlineStr">
+        <is>
+          <t>Ce n'est pas ce qui s'est passé. Isabelle n'a pas été enlevée, et personne ne lui a voulu de mal. Elle a bu la tisane à la valériane du botaniste, dont le dosage était bien trop fort. Épuisée, elle est retournée à la serre pour l'avertir, et s'y est endormie. Elle dormait, à deux pas de vous, pendant que vous la cherchiez.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="520" windowWidth="28800" windowHeight="15900" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Lisez-moi" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Parcours" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Textes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Quiz" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Pop quiz" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Denouements" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lisez-moi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parcours" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Textes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quiz" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pop quiz" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Denouements" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="F10" s="38" t="inlineStr">
         <is>
-          <t>Rendez-vous au bureau des soigneurs pour interroger votre premier témoin.</t>
+          <t>Rendez-vous au bureau des soigneurs, à côté des ours polaires, pour interroger votre premier témoin.</t>
         </is>
       </c>
       <c r="G10" s="37" t="n"/>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="F16" s="40" t="inlineStr">
         <is>
-          <t>Rendez-vous au niveau de l'enclos des loups pour la suite de l'enquête</t>
+          <t>Rendez-vous au niveau du haut de l'enclos des loups pour la suite de l'enquête</t>
         </is>
       </c>
       <c r="G16" s="40" t="n"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="F20" s="37" t="inlineStr">
         <is>
-          <t>Rendez-vous au niveau de l'enclos des loups pour la suite de l'enquête</t>
+          <t>Rendez-vous au niveau du haut de l'enclos des loups pour la suite de l'enquête</t>
         </is>
       </c>
       <c r="G20" s="37" t="n"/>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F23" s="38" t="inlineStr">
         <is>
-          <t>Rendez-vous au-dessus de l'enclos des loups pour interroger votre prochain témoin</t>
+          <t>Rendez-vous au fond de l'impasse, au-dessus de l'enclos des loups, pour interroger votre prochain témoin</t>
         </is>
       </c>
       <c r="G23" s="37" t="n"/>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="F24" s="45" t="inlineStr">
         <is>
-          <t>Rendez-vous au-dessus de l'enclos des loups pour interroger votre prochain témoin</t>
+          <t>Rendez-vous au fond de l'impasse, au-dessus de l'enclos des loups, pour interroger votre prochain témoin</t>
         </is>
       </c>
       <c r="G24" s="43" t="n"/>

--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F40" s="45" t="inlineStr">
         <is>
-          <t>Vous avez désormais intérrogé tous les témoins officiels. Analysez les 4 lettres que vous avez trouvé pour continuer votre enquête.</t>
+          <t>Vous avez désormais interrogé tous les témoins officiels. Notez le mot formé par les 4 lettres que vous avez trouvées.</t>
         </is>
       </c>
       <c r="G40" s="43" t="n"/>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="F43" s="38" t="inlineStr">
         <is>
-          <t>Rendez-vous dans la grande volière pour interroger Bill.</t>
+          <t>Traversez la grande volière pour rencontrer Bill.</t>
         </is>
       </c>
       <c r="G43" s="37" t="n"/>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="F58" s="37" t="inlineStr">
         <is>
-          <t>Vous avez désormais intérrogé tous les témoins officiels. Analysez les 4 lettres que vous avez trouvé pour continuer votre enquête.</t>
+          <t>Vous avez désormais interrogé tous les témoins officiels. Notez le mot formé par les 4 lettres que vous avez trouvées.</t>
         </is>
       </c>
       <c r="G58" s="37" t="n"/>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>"…", botaniste au Parc Zoologique et Botanique de Mulhouse</t>
+          <t>Louis, botaniste au Parc Zoologique &amp; Botanique de Mulhouse</t>
         </is>
       </c>
       <c r="G61" s="12" t="n"/>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="F71" s="38" t="inlineStr">
         <is>
-          <t>Rendez-vous dans la grande volière pour interroger Bill.</t>
+          <t>Traversez la grande volière pour rencontrer Bill.</t>
         </is>
       </c>
       <c r="G71" s="37" t="n"/>

--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -4030,7 +4030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0:35</t>
+          <t>0:26</t>
         </is>
       </c>
       <c r="C3" s="52" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0:54</t>
+          <t>0:45</t>
         </is>
       </c>
       <c r="C4" s="52" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1:13</t>
+          <t>1:20</t>
         </is>
       </c>
       <c r="C5" s="52" t="inlineStr">
@@ -4190,26 +4190,26 @@
       </c>
       <c r="D5" s="52" t="inlineStr">
         <is>
-          <t>Frédéric, 54 ans, qui part en fou rire</t>
+          <t>Une porte qui grince</t>
         </is>
       </c>
       <c r="E5" s="52" t="inlineStr">
         <is>
-          <t>Un dindon qui glousse</t>
+          <t>Un alligator</t>
         </is>
       </c>
       <c r="F5" s="52" t="inlineStr">
         <is>
-          <t>Un singe</t>
+          <t>Un marteau-piqueur</t>
         </is>
       </c>
       <c r="G5" s="52" t="inlineStr">
         <is>
-          <t>Une personne qui s'esclaffe</t>
+          <t>Une otarie</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1:39</t>
+          <t>2:13</t>
         </is>
       </c>
       <c r="C6" s="52" t="inlineStr">
@@ -4230,26 +4230,26 @@
       </c>
       <c r="D6" s="52" t="inlineStr">
         <is>
-          <t>Chewbacca</t>
+          <t>C'est de la techno !</t>
         </is>
       </c>
       <c r="E6" s="52" t="inlineStr">
         <is>
-          <t>Un rhinocéros</t>
+          <t>Un vautour</t>
         </is>
       </c>
       <c r="F6" s="52" t="inlineStr">
         <is>
-          <t>Une personne qui ronfle</t>
+          <t>Un flamant rose</t>
         </is>
       </c>
       <c r="G6" s="52" t="inlineStr">
         <is>
-          <t>Un tigre</t>
+          <t>Un manchot</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2:03</t>
+          <t>3:13</t>
         </is>
       </c>
       <c r="C7" s="52" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="D7" s="52" t="inlineStr">
         <is>
-          <t>Une porte qui grince</t>
+          <t>Une femme qui crie de détresse</t>
         </is>
       </c>
       <c r="E7" s="52" t="inlineStr">
         <is>
-          <t>Un alligator</t>
+          <t>Un renard</t>
         </is>
       </c>
       <c r="F7" s="52" t="inlineStr">
         <is>
-          <t>Un marteau-piqueur</t>
+          <t>Une souricette</t>
         </is>
       </c>
       <c r="G7" s="52" t="inlineStr">
         <is>
-          <t>Une otarie</t>
+          <t>Un corbeau</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2:58</t>
+          <t>3:57</t>
         </is>
       </c>
       <c r="C8" s="52" t="inlineStr">
@@ -4310,108 +4310,30 @@
       </c>
       <c r="D8" s="52" t="inlineStr">
         <is>
-          <t>C'est de la techno !</t>
+          <t>Un zèbre</t>
         </is>
       </c>
       <c r="E8" s="52" t="inlineStr">
         <is>
-          <t>Un vautour</t>
+          <t>Un gecko</t>
         </is>
       </c>
       <c r="F8" s="52" t="inlineStr">
         <is>
-          <t>Un flamant rose</t>
+          <t>Une alarme de voiture de police</t>
         </is>
       </c>
       <c r="G8" s="52" t="inlineStr">
         <is>
-          <t>Un manchot</t>
+          <t>Une sonnerie de téléphone</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>E06</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3:59</t>
-        </is>
-      </c>
-      <c r="C9" s="52" t="inlineStr">
-        <is>
-          <t>Bruit d'humain ou d'animal ?</t>
-        </is>
-      </c>
-      <c r="D9" s="52" t="inlineStr">
-        <is>
-          <t>Une femme qui crie de détresse</t>
-        </is>
-      </c>
-      <c r="E9" s="52" t="inlineStr">
-        <is>
-          <t>Un renard</t>
-        </is>
-      </c>
-      <c r="F9" s="52" t="inlineStr">
-        <is>
-          <t>Une souricette</t>
-        </is>
-      </c>
-      <c r="G9" s="52" t="inlineStr">
-        <is>
-          <t>Un corbeau</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>E06</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>4:42</t>
-        </is>
-      </c>
-      <c r="C10" s="52" t="inlineStr">
-        <is>
-          <t>Bruit d'humain ou d'animal ?</t>
-        </is>
-      </c>
-      <c r="D10" s="52" t="inlineStr">
-        <is>
-          <t>Un zèbre</t>
-        </is>
-      </c>
-      <c r="E10" s="52" t="inlineStr">
-        <is>
-          <t>Un gecko</t>
-        </is>
-      </c>
-      <c r="F10" s="52" t="inlineStr">
-        <is>
-          <t>Une alarme de voiture de police</t>
-        </is>
-      </c>
-      <c r="G10" s="52" t="inlineStr">
-        <is>
-          <t>Une sonnerie de téléphone</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="9" ht="30" customHeight="1"/>
+    <row r="10" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -4030,7 +4030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="C3" s="50" t="inlineStr">
         <is>
-          <t>tisane|valeriane|infusion|plante;endorm|sommeil|assoupi|dort|dormi;serre</t>
+          <t>tisane|valeriane|infusion|plante|breuvage|boisson|somnifere;endorm|sommeil|assoupi|dort|dormi|somnol|sieste;serre</t>
         </is>
       </c>
       <c r="D3" s="50" t="inlineStr">

--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -1696,7 +1696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3909,20 +3909,20 @@
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>5. Finish</t>
+          <t>5. Photo : l'aveu de Greg</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>Message final à délivrer en fonction des conclusions du groupe dans le champs IA</t>
-        </is>
-      </c>
-      <c r="F68" s="12" t="n"/>
-      <c r="G68" s="12" t="inlineStr">
-        <is>
-          <t>3 messages de félicitations (parfait - presque - dommage)</t>
-        </is>
-      </c>
+          <t>La legende sous la photo de l'aveu. Une ligne.</t>
+        </is>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>Une dernière pièce au dossier : l'aveu de Greg.</t>
+        </is>
+      </c>
+      <c r="G68" s="12" t="n"/>
     </row>
     <row r="69" ht="30" customFormat="1" customHeight="1" s="39">
       <c r="A69" s="34" t="inlineStr">
@@ -4018,6 +4018,38 @@
         </is>
       </c>
       <c r="G71" s="37" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>La serre</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>les deux</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>6. Fin</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Le mot de la fin, au-dessus des remerciements et des partenaires.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>L'affaire est classée.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -3435,7 +3435,7 @@
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>3. Texte ou epreuve</t>
+          <t>3. Les images du commissaire</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
@@ -3445,14 +3445,10 @@
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G54" s="12" t="inlineStr">
-        <is>
-          <t>Fichier audio</t>
-        </is>
-      </c>
+          <t>Le commissaire vous a envoyé 4 images.</t>
+        </is>
+      </c>
+      <c r="G54" s="12" t="n"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="37" t="inlineStr">

--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -2398,7 +2398,7 @@
       </c>
       <c r="F22" s="34" t="inlineStr">
         <is>
-          <t>Observez l'enclos à l'aide des jumelles à la recherche d'un objet qui n'est pas à sa place. Vous trouverez un indice sur cet objet, à noter soigneusement.</t>
+          <t>Observez l'enclos à la recherche d'un objet qui n'est pas à sa place. Vous trouverez un indice sur cet objet, à noter soigneusement.</t>
         </is>
       </c>
       <c r="G22" s="34" t="n"/>

--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -3845,12 +3845,12 @@
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
-          <t>Veuillez nous donner les conclusions de votr enquête. Qu'est arrivé à Isabelle ?</t>
+          <t>Qu'est-il arrivé à Isabelle ?</t>
         </is>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>Champ IA pour donner ses conclusions</t>
+          <t>Choix multiple : les quatre propositions sont dans CONCLUSIONS_QCM (fabriquer-les-pages.py)</t>
         </is>
       </c>
     </row>
@@ -3905,17 +3905,17 @@
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>5. Photo : l'aveu de Greg</t>
+          <t>5. Photo : la lettre de Greg</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>La legende sous la photo de l'aveu. Une ligne.</t>
+          <t>La legende sous la photo de la lettre. Une ligne.</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
         <is>
-          <t>Une dernière pièce au dossier : l'aveu de Greg.</t>
+          <t>Une dernière pièce au dossier : la lettre de Greg.</t>
         </is>
       </c>
       <c r="G68" s="12" t="n"/>

--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -4792,7 +4792,7 @@
       </c>
       <c r="F5" s="50" t="inlineStr">
         <is>
-          <t>Ce n'est pas ce qui s'est passé. Isabelle n'a pas été enlevée, et personne ne lui a voulu de mal. Elle a bu la tisane à la valériane du botaniste, dont le dosage était bien trop fort. Épuisée, elle est retournée à la serre pour l'avertir, et s'y est endormie. Elle dormait, à deux pas de vous, pendant que vous la cherchiez.</t>
+          <t>Ce n'est pas ce qui s'est passé. Personne ne lui a voulu de mal, et il ne lui est rien arrivé de grave. Elle a bu la tisane à la valériane du botaniste, dont le dosage était bien trop fort. Épuisée, elle est retournée à la serre pour l'avertir, et s'y est endormie. Elle dormait, à deux pas de vous, pendant que vous la cherchiez.</t>
         </is>
       </c>
     </row>

--- a/contenu/sanctuaire-cahier-de-contenu.xlsx
+++ b/contenu/sanctuaire-cahier-de-contenu.xlsx
@@ -1775,12 +1775,12 @@
       </c>
       <c r="E3" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Une page de texte avec le chrono qui se lance, le logo du jeu et une photo d'arrière plan. </t>
+          <t xml:space="preserve">Une page de texte le logo du jeu et une photo d'arrière plan. </t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>Bienvenue au Parc Zoologique &amp; Botanique de Mulhouse. Vous êtes sur le point de prendre part à une expérience unique en son genre : une enquête de police grandeur nature. Armez-vous de bon sens et observez bien ce qu'il se passe autour de vous. Suivez les consignes qui vous sont données et respectez le sens des énigmes qui vous est proposé. Vous avez 3 heures à partir de maintenant pour terminer l'enquête. Cliquez sur suivant pour démarrer votre enquête.</t>
+          <t>Bienvenue au Parc Zoologique &amp; Botanique de Mulhouse. Vous êtes sur le point de prendre part à une expérience unique en son genre : une enquête de police grandeur nature. Armez-vous de bon sens et observez bien ce qu'il se passe autour de vous. Suivez les consignes qui vous sont données et respectez le sens des énigmes qui vous est proposé. Prenez votre temps : votre enquête reste ouverte jusqu'à la fin de la journée. Cliquez sur suivant pour démarrer votre enquête.</t>
         </is>
       </c>
       <c r="G3" s="29" t="n"/>
